--- a/대시보드_구축_데이터.xlsx
+++ b/대시보드_구축_데이터.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\dashboard\dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\dashboard_v2\dashboard_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E234408E-C411-4465-B95E-861C54A2E485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D097E2C2-C7BC-4E7E-9479-1F6A9FED53C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3F0FD738-DFD1-4862-A6F4-1A909B15B620}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3F0FD738-DFD1-4862-A6F4-1A909B15B620}"/>
   </bookViews>
   <sheets>
     <sheet name="유형분류" sheetId="4" r:id="rId1"/>
@@ -884,7 +884,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -892,8 +892,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1132,10 +1133,29 @@
     <xf numFmtId="181" fontId="3" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="179" fontId="3" fillId="3" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="3" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="13" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="3" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준_Sheet1" xfId="1" xr:uid="{5622930D-9C9B-4BE7-85F7-8246D9E981FD}"/>
+    <cellStyle name="표준_Sheet2" xfId="5" xr:uid="{83D124FB-51B5-44BA-AEF4-D0FDDA39DE66}"/>
     <cellStyle name="표준_Sheet2_1" xfId="2" xr:uid="{4F2AD0DF-6CF3-4388-82C8-2AEF0A46D7ED}"/>
     <cellStyle name="표준_문항" xfId="3" xr:uid="{C2D4C164-159A-49AE-86E6-079E3875562A}"/>
     <cellStyle name="표준_영역" xfId="4" xr:uid="{36A58803-0718-48BC-B017-9D000CBA22BC}"/>
@@ -3443,10 +3463,10 @@
         <v>0.4119061381755153</v>
       </c>
       <c r="G3" s="8">
-        <v>3.87</v>
+        <v>3.8703703703703702</v>
       </c>
       <c r="H3" s="8">
-        <v>0.37373787605753861</v>
+        <v>0.43555933482865294</v>
       </c>
       <c r="I3" s="9">
         <v>2.3666666666666671</v>
@@ -3493,10 +3513,10 @@
         <v>0.48458622506609622</v>
       </c>
       <c r="G4" s="8">
-        <v>3.9671428571428571</v>
+        <v>3.9999999999999996</v>
       </c>
       <c r="H4" s="8">
-        <v>0.52114343149508868</v>
+        <v>0.62195761569432084</v>
       </c>
       <c r="I4" s="9">
         <v>2.7428571428571424</v>
@@ -3543,10 +3563,10 @@
         <v>0.5026245403593308</v>
       </c>
       <c r="G5" s="8">
-        <v>4.2613333333333339</v>
+        <v>4.3777777777777782</v>
       </c>
       <c r="H5" s="8">
-        <v>0.42365529563999266</v>
+        <v>0.51055870769533185</v>
       </c>
       <c r="I5" s="9">
         <v>2.6</v>
@@ -3593,10 +3613,10 @@
         <v>0.43692104549906963</v>
       </c>
       <c r="G6" s="8">
-        <v>3.6659999999999999</v>
+        <v>3.5333333333333332</v>
       </c>
       <c r="H6" s="8">
-        <v>0.40147229045103461</v>
+        <v>0.31817380140614115</v>
       </c>
       <c r="I6" s="9">
         <v>2.5599999999999996</v>
@@ -3643,10 +3663,10 @@
         <v>0.77731803872889338</v>
       </c>
       <c r="G7" s="8">
-        <v>4.0659999999999998</v>
+        <v>3.9777777777777779</v>
       </c>
       <c r="H7" s="8">
-        <v>0.45670802732404675</v>
+        <v>0.41837099989460569</v>
       </c>
       <c r="I7" s="9">
         <v>2.2199999999999998</v>
@@ -3693,10 +3713,10 @@
         <v>0.56144312477128178</v>
       </c>
       <c r="G8" s="8">
-        <v>3.9864705882352944</v>
+        <v>4.0130718954248366</v>
       </c>
       <c r="H8" s="8">
-        <v>0.43587471216610219</v>
+        <v>0.45113429220197943</v>
       </c>
       <c r="I8" s="9">
         <v>2.8588235294117652</v>
@@ -3743,10 +3763,10 @@
         <v>0.22803508501982761</v>
       </c>
       <c r="G9" s="8">
-        <v>3.69</v>
+        <v>3.6444444444444444</v>
       </c>
       <c r="H9" s="8">
-        <v>0.61725197448043845</v>
+        <v>0.68222584146705578</v>
       </c>
       <c r="I9" s="9">
         <v>2.76</v>
@@ -3793,10 +3813,10 @@
         <v>0.34941856466612276</v>
       </c>
       <c r="G10" s="8">
-        <v>3.9000000000000004</v>
+        <v>3.9222222222222216</v>
       </c>
       <c r="H10" s="8">
-        <v>0.3836665218650176</v>
+        <v>0.37423905419464071</v>
       </c>
       <c r="I10" s="9">
         <v>2.8200000000000003</v>
@@ -3843,10 +3863,10 @@
         <v>0.68977466676378529</v>
       </c>
       <c r="G11" s="8">
-        <v>3.6854545454545455</v>
+        <v>3.6868686868686869</v>
       </c>
       <c r="H11" s="8">
-        <v>0.59830366263902546</v>
+        <v>0.60617843972351437</v>
       </c>
       <c r="I11" s="9">
         <v>2.7090909090909094</v>
@@ -3893,10 +3913,10 @@
         <v>0.85884774229454919</v>
       </c>
       <c r="G12" s="8">
-        <v>3.6044444444444443</v>
+        <v>3.5061728395061729</v>
       </c>
       <c r="H12" s="8">
-        <v>0.90576088333388416</v>
+        <v>0.92314396893440864</v>
       </c>
       <c r="I12" s="9">
         <v>2.4888888888888889</v>
@@ -3943,10 +3963,10 @@
         <v>0.46715450691750088</v>
       </c>
       <c r="G13" s="8">
-        <v>3.8133333333333335</v>
+        <v>3.5185185185185186</v>
       </c>
       <c r="H13" s="8">
-        <v>0.5589573627150225</v>
+        <v>0.46259244432580721</v>
       </c>
       <c r="I13" s="9">
         <v>2.6</v>
@@ -3993,10 +4013,10 @@
         <v>0.53996472547927121</v>
       </c>
       <c r="G14" s="8">
-        <v>3.8581818181818184</v>
+        <v>3.8989898989898988</v>
       </c>
       <c r="H14" s="8">
-        <v>0.53988214202057783</v>
+        <v>0.67621825170413041</v>
       </c>
       <c r="I14" s="9">
         <v>2.4454545454545453</v>
@@ -4043,10 +4063,10 @@
         <v>0.49260531868829832</v>
       </c>
       <c r="G15" s="8">
-        <v>3.6593333333333335</v>
+        <v>3.6888888888888891</v>
       </c>
       <c r="H15" s="8">
-        <v>0.53566336265908476</v>
+        <v>0.61319989346659431</v>
       </c>
       <c r="I15" s="9">
         <v>2.5333333333333332</v>
@@ -4093,10 +4113,10 @@
         <v>0.5972879045394196</v>
       </c>
       <c r="G16" s="8">
-        <v>3.812121212121212</v>
+        <v>3.8585858585858581</v>
       </c>
       <c r="H16" s="8">
-        <v>0.65263292504169956</v>
+        <v>0.81662543701326396</v>
       </c>
       <c r="I16" s="9">
         <v>2.69090909090909</v>
@@ -4143,10 +4163,10 @@
         <v>0.61372399566673519</v>
       </c>
       <c r="G17" s="8">
-        <v>3.96</v>
+        <v>4.0396825396825404</v>
       </c>
       <c r="H17" s="8">
-        <v>0.73838701547046781</v>
+        <v>0.86792276151543968</v>
       </c>
       <c r="I17" s="9">
         <v>2.7285714285714286</v>
@@ -4193,10 +4213,10 @@
         <v>0.61682250283205442</v>
       </c>
       <c r="G18" s="8">
-        <v>4.1779999999999999</v>
+        <v>4.1777777777777771</v>
       </c>
       <c r="H18" s="8">
-        <v>0.31987497557639599</v>
+        <v>0.44859176084858565</v>
       </c>
       <c r="I18" s="9">
         <v>2.6</v>
@@ -4243,10 +4263,10 @@
         <v>0.51713312277078771</v>
       </c>
       <c r="G19" s="8">
-        <v>3.59</v>
+        <v>3.5666666666666664</v>
       </c>
       <c r="H19" s="8">
-        <v>0.71538645344860852</v>
+        <v>0.80029144211233705</v>
       </c>
       <c r="I19" s="9">
         <v>2.76</v>
@@ -4293,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>3.56</v>
+        <v>3.5555555555555554</v>
       </c>
       <c r="H20" s="12">
         <v>0</v>
@@ -4343,10 +4363,10 @@
         <v>0.41276843117876366</v>
       </c>
       <c r="G21" s="8">
-        <v>3.6669999999999998</v>
+        <v>3.6</v>
       </c>
       <c r="H21" s="8">
-        <v>0.76852022311279056</v>
+        <v>0.82850452810254438</v>
       </c>
       <c r="I21" s="9">
         <v>3.3199999999999994</v>
@@ -4393,10 +4413,10 @@
         <v>0.35953673896650196</v>
       </c>
       <c r="G22" s="8">
-        <v>3.6399999999999997</v>
+        <v>3.6944444444444446</v>
       </c>
       <c r="H22" s="8">
-        <v>0.77356318423254844</v>
+        <v>1.0198644305936566</v>
       </c>
       <c r="I22" s="9">
         <v>2.95</v>
@@ -4446,7 +4466,7 @@
         <v>3.75</v>
       </c>
       <c r="H23" s="8">
-        <v>0.60818230349601132</v>
+        <v>0.81595639126824604</v>
       </c>
       <c r="I23" s="9">
         <v>2.7250000000000001</v>
@@ -4493,10 +4513,10 @@
         <v>0.62269140731552464</v>
       </c>
       <c r="G24" s="8">
-        <v>3.6927272727272729</v>
+        <v>3.7323232323232318</v>
       </c>
       <c r="H24" s="8">
-        <v>0.67723655442492936</v>
+        <v>0.76801054742191655</v>
       </c>
       <c r="I24" s="9">
         <v>2.9818181818181815</v>
@@ -4543,10 +4563,10 @@
         <v>0.21361179742701455</v>
       </c>
       <c r="G25" s="8">
-        <v>3.246</v>
+        <v>3.1555555555555554</v>
       </c>
       <c r="H25" s="8">
-        <v>0.51169326749528377</v>
+        <v>0.69210717788433052</v>
       </c>
       <c r="I25" s="9">
         <v>3.52</v>
@@ -4593,10 +4613,10 @@
         <v>0.63215120937569313</v>
       </c>
       <c r="G26" s="8">
-        <v>3.8158333333333339</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="H26" s="8">
-        <v>0.691131592960327</v>
+        <v>0.78352852357159342</v>
       </c>
       <c r="I26" s="9">
         <v>2.7166666666666668</v>
@@ -4643,10 +4663,10 @@
         <v>0.92303846073714624</v>
       </c>
       <c r="G27" s="8">
-        <v>3.6219999999999999</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="H27" s="8">
-        <v>0.50071948234515518</v>
+        <v>0.67128033186636504</v>
       </c>
       <c r="I27" s="9">
         <v>2.84</v>
@@ -4693,10 +4713,10 @@
         <v>0.94438869116481894</v>
       </c>
       <c r="G28" s="8">
-        <v>3.7540000000000004</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="H28" s="8">
-        <v>0.59378447268348145</v>
+        <v>0.78173595997057166</v>
       </c>
       <c r="I28" s="9">
         <v>2.48</v>
@@ -4743,10 +4763,10 @@
         <v>1.0889444430272834</v>
       </c>
       <c r="G29" s="8">
-        <v>3.9400000000000004</v>
+        <v>4.0555555555555554</v>
       </c>
       <c r="H29" s="8">
-        <v>0.70710678118654779</v>
+        <v>1.1785113019775795</v>
       </c>
       <c r="I29" s="9">
         <v>3</v>
@@ -4796,7 +4816,7 @@
         <v>4.25</v>
       </c>
       <c r="H30" s="8">
-        <v>0.57745748142797737</v>
+        <v>0.73162378898358804</v>
       </c>
       <c r="I30" s="9">
         <v>2.7750000000000004</v>
@@ -4843,10 +4863,10 @@
         <v>0.64034345752083988</v>
       </c>
       <c r="G31" s="8">
-        <v>3.7361538461538459</v>
+        <v>3.6495726495726495</v>
       </c>
       <c r="H31" s="8">
-        <v>0.59628766074687012</v>
+        <v>0.70978776438125313</v>
       </c>
       <c r="I31" s="9">
         <v>2.6</v>
@@ -4893,10 +4913,10 @@
         <v>0.68397855716876588</v>
       </c>
       <c r="G32" s="8">
-        <v>3.6466666666666669</v>
+        <v>3.574074074074074</v>
       </c>
       <c r="H32" s="8">
-        <v>0.76505337504429516</v>
+        <v>0.74507988358417676</v>
       </c>
       <c r="I32" s="9">
         <v>2.0333333333333332</v>
@@ -4943,10 +4963,10 @@
         <v>0.5747012410131741</v>
       </c>
       <c r="G33" s="8">
-        <v>3.9596296296296307</v>
+        <v>3.9176954732510292</v>
       </c>
       <c r="H33" s="8">
-        <v>0.58513008701327462</v>
+        <v>0.65260687273797024</v>
       </c>
       <c r="I33" s="9">
         <v>2.6185185185185182</v>
@@ -4993,10 +5013,10 @@
         <v>0.46841678632846373</v>
       </c>
       <c r="G34" s="8">
-        <v>3.4771428571428573</v>
+        <v>3.6031746031746033</v>
       </c>
       <c r="H34" s="8">
-        <v>0.41503872452717328</v>
+        <v>0.56239180159988156</v>
       </c>
       <c r="I34" s="9">
         <v>2.2571428571428571</v>
@@ -5043,10 +5063,10 @@
         <v>0.4372184808536802</v>
       </c>
       <c r="G35" s="8">
-        <v>3.9340000000000002</v>
+        <v>3.9777777777777774</v>
       </c>
       <c r="H35" s="8">
-        <v>0.53281641616351616</v>
+        <v>0.4823354250696209</v>
       </c>
       <c r="I35" s="9">
         <v>2.2800000000000002</v>
@@ -5093,10 +5113,10 @@
         <v>0.36636730203444751</v>
       </c>
       <c r="G36" s="8">
-        <v>3.8624999999999998</v>
+        <v>3.6388888888888888</v>
       </c>
       <c r="H36" s="8">
-        <v>0.68839789850541155</v>
+        <v>0.53958526979012822</v>
       </c>
       <c r="I36" s="9">
         <v>3</v>
@@ -5143,10 +5163,10 @@
         <v>0.6761993725210409</v>
       </c>
       <c r="G37" s="8">
-        <v>3.8864516129032256</v>
+        <v>3.8781362007168458</v>
       </c>
       <c r="H37" s="8">
-        <v>0.54063264414385703</v>
+        <v>0.603388810429208</v>
       </c>
       <c r="I37" s="9">
         <v>2.8774193548387101</v>
@@ -5193,10 +5213,10 @@
         <v>0.53305255767116067</v>
       </c>
       <c r="G38" s="8">
-        <v>3.432631578947368</v>
+        <v>3.3508771929824559</v>
       </c>
       <c r="H38" s="8">
-        <v>0.37079257611624872</v>
+        <v>0.39763215124279239</v>
       </c>
       <c r="I38" s="9">
         <v>2.9684210526315788</v>
@@ -5243,10 +5263,10 @@
         <v>0.49761933242188244</v>
       </c>
       <c r="G39" s="8">
-        <v>3.8144444444444439</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="H39" s="8">
-        <v>0.51322780300542736</v>
+        <v>0.52411006289203366</v>
       </c>
       <c r="I39" s="9">
         <v>2.911111111111111</v>
@@ -5293,10 +5313,10 @@
         <v>0.54392587467674036</v>
       </c>
       <c r="G40" s="8">
-        <v>3.5425000000000004</v>
+        <v>3.3472222222222223</v>
       </c>
       <c r="H40" s="8">
-        <v>0.52215897962210689</v>
+        <v>0.45788217333292702</v>
       </c>
       <c r="I40" s="9">
         <v>3.15</v>
@@ -5343,10 +5363,10 @@
         <v>0.65427568093783406</v>
       </c>
       <c r="G41" s="8">
-        <v>3.7570000000000006</v>
+        <v>3.6222222222222218</v>
       </c>
       <c r="H41" s="8">
-        <v>0.59552124693881014</v>
+        <v>0.70116501133032505</v>
       </c>
       <c r="I41" s="9">
         <v>3</v>
@@ -5393,10 +5413,10 @@
         <v>0.51344912114054708</v>
       </c>
       <c r="G42" s="8">
-        <v>3.7119999999999997</v>
+        <v>3.4888888888888885</v>
       </c>
       <c r="H42" s="8">
-        <v>0.38035509724466671</v>
+        <v>0.2897423291201176</v>
       </c>
       <c r="I42" s="9">
         <v>2.96</v>
@@ -5443,10 +5463,10 @@
         <v>0.49533778758492059</v>
       </c>
       <c r="G43" s="8">
-        <v>3.5463636363636364</v>
+        <v>3.5555555555555554</v>
       </c>
       <c r="H43" s="8">
-        <v>0.58768752188269524</v>
+        <v>0.65689487435610305</v>
       </c>
       <c r="I43" s="9">
         <v>2.8636363636363633</v>
@@ -5493,10 +5513,10 @@
         <v>0.55817722829027905</v>
       </c>
       <c r="G44" s="8">
-        <v>4.0999999999999996</v>
+        <v>4.1414141414141419</v>
       </c>
       <c r="H44" s="8">
-        <v>0.47673892226248965</v>
+        <v>0.59231896039359655</v>
       </c>
       <c r="I44" s="9">
         <v>3.2727272727272725</v>
@@ -5543,10 +5563,10 @@
         <v>0.62792495060297082</v>
       </c>
       <c r="G45" s="8">
-        <v>3.8207692307692311</v>
+        <v>3.7179487179487181</v>
       </c>
       <c r="H45" s="8">
-        <v>0.64707626467650037</v>
+        <v>0.79558372676092348</v>
       </c>
       <c r="I45" s="9">
         <v>2.7230769230769232</v>
@@ -5593,10 +5613,10 @@
         <v>0.60480942820399597</v>
       </c>
       <c r="G46" s="8">
-        <v>4.137777777777778</v>
+        <v>4.382716049382716</v>
       </c>
       <c r="H46" s="8">
-        <v>0.41490293376215631</v>
+        <v>0.53028966901023544</v>
       </c>
       <c r="I46" s="9">
         <v>4.0222222222222221</v>
@@ -5643,10 +5663,10 @@
         <v>0.66902380910013759</v>
       </c>
       <c r="G47" s="8">
-        <v>3.9724999999999997</v>
+        <v>4.3055555555555554</v>
       </c>
       <c r="H47" s="8">
-        <v>0.5121035051627747</v>
+        <v>0.6164986186012209</v>
       </c>
       <c r="I47" s="9">
         <v>3.8</v>
@@ -5693,10 +5713,10 @@
         <v>0.73368309452438873</v>
       </c>
       <c r="G48" s="8">
-        <v>4.206666666666667</v>
+        <v>4.378600823045268</v>
       </c>
       <c r="H48" s="8">
-        <v>0.51622892953834709</v>
+        <v>0.54017975557899089</v>
       </c>
       <c r="I48" s="9">
         <v>3.9629629629629619</v>
@@ -5743,10 +5763,10 @@
         <v>0.55802734000685117</v>
       </c>
       <c r="G49" s="8">
-        <v>4.2475609756097574</v>
+        <v>4.4905149051490501</v>
       </c>
       <c r="H49" s="8">
-        <v>0.431866764684462</v>
+        <v>0.55886547872116166</v>
       </c>
       <c r="I49" s="9">
         <v>3.6926829268292689</v>
@@ -5793,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="8">
-        <v>3.67</v>
+        <v>4.1111111111111107</v>
       </c>
       <c r="H50" s="12">
         <v>0</v>
@@ -5843,10 +5863,10 @@
         <v>0.4729429141027488</v>
       </c>
       <c r="G51" s="8">
-        <v>3.6177777777777775</v>
+        <v>3.7160493827160495</v>
       </c>
       <c r="H51" s="8">
-        <v>0.95121997689516802</v>
+        <v>1.0958833055935921</v>
       </c>
       <c r="I51" s="9">
         <v>3.1111111111111112</v>
@@ -5893,10 +5913,10 @@
         <v>0.388829746069628</v>
       </c>
       <c r="G52" s="15">
-        <v>4.1720000000000006</v>
+        <v>4.4962962962962951</v>
       </c>
       <c r="H52" s="15">
-        <v>0.50349067234940603</v>
+        <v>0.57100219248377804</v>
       </c>
       <c r="I52" s="16">
         <v>3.8799999999999994</v>
@@ -5943,10 +5963,10 @@
         <v>0.64800000000000002</v>
       </c>
       <c r="G53" s="53">
-        <v>3.87</v>
+        <v>3.9034369885433704</v>
       </c>
       <c r="H53" s="54">
-        <v>0.59499999999999997</v>
+        <v>0.70378635042468374</v>
       </c>
       <c r="I53" s="53">
         <v>2.92</v>
@@ -5976,6 +5996,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7111,10 +7132,10 @@
       <c r="BL3" s="22">
         <v>0.63245553203367588</v>
       </c>
-      <c r="BM3" s="23">
+      <c r="BM3" s="82">
         <v>3</v>
       </c>
-      <c r="BN3" s="22">
+      <c r="BN3" s="83">
         <v>0.89442719099991586</v>
       </c>
       <c r="BO3" s="23">
@@ -7154,10 +7175,10 @@
         <v>1.51657508881031</v>
       </c>
       <c r="CA3" s="23">
-        <v>3.87</v>
+        <v>3.8703703703703702</v>
       </c>
       <c r="CB3" s="22">
-        <v>0.37373787605753861</v>
+        <v>0.43555933482865294</v>
       </c>
       <c r="CC3" s="23">
         <v>2.666666666666667</v>
@@ -7576,10 +7597,10 @@
       <c r="BL4" s="26">
         <v>0.89973541084243724</v>
       </c>
-      <c r="BM4" s="27">
-        <v>2.8571428571428572</v>
-      </c>
-      <c r="BN4" s="26">
+      <c r="BM4" s="84">
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="BN4" s="85">
         <v>1.3451854182690985</v>
       </c>
       <c r="BO4" s="27">
@@ -7619,10 +7640,10 @@
         <v>0.95118973121134176</v>
       </c>
       <c r="CA4" s="27">
-        <v>3.9671428571428571</v>
+        <v>3.9999999999999996</v>
       </c>
       <c r="CB4" s="26">
-        <v>0.52114343149508868</v>
+        <v>0.62195761569432084</v>
       </c>
       <c r="CC4" s="27">
         <v>3.2857142857142856</v>
@@ -8041,10 +8062,10 @@
       <c r="BL5" s="26">
         <v>0.7988086367179803</v>
       </c>
-      <c r="BM5" s="27">
-        <v>2.4666666666666668</v>
-      </c>
-      <c r="BN5" s="26">
+      <c r="BM5" s="84">
+        <v>3.5333333333333332</v>
+      </c>
+      <c r="BN5" s="85">
         <v>1.0600988273786192</v>
       </c>
       <c r="BO5" s="27">
@@ -8084,10 +8105,10 @@
         <v>0.5163977794943222</v>
       </c>
       <c r="CA5" s="27">
-        <v>4.2613333333333339</v>
+        <v>4.3777777777777782</v>
       </c>
       <c r="CB5" s="26">
-        <v>0.42365529563999266</v>
+        <v>0.51055870769533185</v>
       </c>
       <c r="CC5" s="27">
         <v>3.1333333333333333</v>
@@ -8506,10 +8527,10 @@
       <c r="BL6" s="26">
         <v>0.54772255750516607</v>
       </c>
-      <c r="BM6" s="27">
-        <v>3.6</v>
-      </c>
-      <c r="BN6" s="26">
+      <c r="BM6" s="84">
+        <v>2.4</v>
+      </c>
+      <c r="BN6" s="85">
         <v>1.1401754250991378</v>
       </c>
       <c r="BO6" s="27">
@@ -8549,10 +8570,10 @@
         <v>0.83666002653407556</v>
       </c>
       <c r="CA6" s="27">
-        <v>3.6659999999999999</v>
+        <v>3.5333333333333332</v>
       </c>
       <c r="CB6" s="26">
-        <v>0.40147229045103461</v>
+        <v>0.31817380140614115</v>
       </c>
       <c r="CC6" s="27">
         <v>3</v>
@@ -8971,10 +8992,10 @@
       <c r="BL7" s="26">
         <v>0.56764621219754663</v>
       </c>
-      <c r="BM7" s="27">
-        <v>3.4000000000000004</v>
-      </c>
-      <c r="BN7" s="26">
+      <c r="BM7" s="84">
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="BN7" s="85">
         <v>1.0749676997731397</v>
       </c>
       <c r="BO7" s="27">
@@ -9014,10 +9035,10 @@
         <v>0.94868329805051388</v>
       </c>
       <c r="CA7" s="27">
-        <v>4.0659999999999998</v>
+        <v>3.9777777777777779</v>
       </c>
       <c r="CB7" s="26">
-        <v>0.45670802732404675</v>
+        <v>0.41837099989460569</v>
       </c>
       <c r="CC7" s="27">
         <v>2.8</v>
@@ -9436,10 +9457,10 @@
       <c r="BL8" s="26">
         <v>0.74754500159640203</v>
       </c>
-      <c r="BM8" s="27">
-        <v>2.8823529411764706</v>
-      </c>
-      <c r="BN8" s="26">
+      <c r="BM8" s="84">
+        <v>3.1176470588235294</v>
+      </c>
+      <c r="BN8" s="85">
         <v>0.99261982533448267</v>
       </c>
       <c r="BO8" s="27">
@@ -9479,10 +9500,10 @@
         <v>1.0606601717798212</v>
       </c>
       <c r="CA8" s="27">
-        <v>3.9864705882352944</v>
+        <v>4.0130718954248366</v>
       </c>
       <c r="CB8" s="26">
-        <v>0.43587471216610219</v>
+        <v>0.45113429220197943</v>
       </c>
       <c r="CC8" s="27">
         <v>3.7647058823529411</v>
@@ -9901,10 +9922,10 @@
       <c r="BL9" s="26">
         <v>0.44721359549995793</v>
       </c>
-      <c r="BM9" s="27">
-        <v>3.2</v>
-      </c>
-      <c r="BN9" s="26">
+      <c r="BM9" s="84">
+        <v>2.8</v>
+      </c>
+      <c r="BN9" s="85">
         <v>0.83666002653407556</v>
       </c>
       <c r="BO9" s="27">
@@ -9944,10 +9965,10 @@
         <v>0.70710678118654757</v>
       </c>
       <c r="CA9" s="27">
-        <v>3.69</v>
+        <v>3.6444444444444444</v>
       </c>
       <c r="CB9" s="26">
-        <v>0.61725197448043845</v>
+        <v>0.68222584146705578</v>
       </c>
       <c r="CC9" s="27">
         <v>3.6</v>
@@ -10366,10 +10387,10 @@
       <c r="BL10" s="26">
         <v>0.47140452079103157</v>
       </c>
-      <c r="BM10" s="27">
-        <v>2.9</v>
-      </c>
-      <c r="BN10" s="26">
+      <c r="BM10" s="84">
+        <v>3.1</v>
+      </c>
+      <c r="BN10" s="85">
         <v>0.73786478737262184</v>
       </c>
       <c r="BO10" s="27">
@@ -10409,10 +10430,10 @@
         <v>0.66666666666666674</v>
       </c>
       <c r="CA10" s="27">
-        <v>3.9000000000000004</v>
+        <v>3.9222222222222216</v>
       </c>
       <c r="CB10" s="26">
-        <v>0.3836665218650176</v>
+        <v>0.37423905419464071</v>
       </c>
       <c r="CC10" s="27">
         <v>3.5</v>
@@ -10831,10 +10852,10 @@
       <c r="BL11" s="26">
         <v>0.90453403373329089</v>
       </c>
-      <c r="BM11" s="27">
+      <c r="BM11" s="84">
         <v>3</v>
       </c>
-      <c r="BN11" s="26">
+      <c r="BN11" s="85">
         <v>0.7745966692414834</v>
       </c>
       <c r="BO11" s="27">
@@ -10874,10 +10895,10 @@
         <v>0.89442719099991586</v>
       </c>
       <c r="CA11" s="27">
-        <v>3.6854545454545455</v>
+        <v>3.6868686868686869</v>
       </c>
       <c r="CB11" s="26">
-        <v>0.59830366263902546</v>
+        <v>0.60617843972351437</v>
       </c>
       <c r="CC11" s="27">
         <v>3.0909090909090908</v>
@@ -11296,10 +11317,10 @@
       <c r="BL12" s="26">
         <v>1.1180339887498949</v>
       </c>
-      <c r="BM12" s="27">
-        <v>3.4444444444444446</v>
-      </c>
-      <c r="BN12" s="26">
+      <c r="BM12" s="84">
+        <v>2.5555555555555554</v>
+      </c>
+      <c r="BN12" s="85">
         <v>1.0137937550497031</v>
       </c>
       <c r="BO12" s="27">
@@ -11339,10 +11360,10 @@
         <v>1.4813657362192649</v>
       </c>
       <c r="CA12" s="27">
-        <v>3.6044444444444443</v>
+        <v>3.5061728395061729</v>
       </c>
       <c r="CB12" s="26">
-        <v>0.90576088333388416</v>
+        <v>0.92314396893440864</v>
       </c>
       <c r="CC12" s="27">
         <v>2.7777777777777777</v>
@@ -11761,10 +11782,10 @@
       <c r="BL13" s="26">
         <v>0.57735026918962573</v>
       </c>
-      <c r="BM13" s="27">
-        <v>4.333333333333333</v>
-      </c>
-      <c r="BN13" s="26">
+      <c r="BM13" s="84">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="BN13" s="85">
         <v>0.57735026918962573</v>
       </c>
       <c r="BO13" s="27">
@@ -11804,10 +11825,10 @@
         <v>1.1547005383792515</v>
       </c>
       <c r="CA13" s="27">
-        <v>3.8133333333333335</v>
+        <v>3.5185185185185186</v>
       </c>
       <c r="CB13" s="26">
-        <v>0.5589573627150225</v>
+        <v>0.46259244432580721</v>
       </c>
       <c r="CC13" s="27">
         <v>4</v>
@@ -12226,10 +12247,10 @@
       <c r="BL14" s="26">
         <v>0.75162162351482753</v>
       </c>
-      <c r="BM14" s="27">
-        <v>2.8181818181818179</v>
-      </c>
-      <c r="BN14" s="26">
+      <c r="BM14" s="84">
+        <v>3.1818181818181821</v>
+      </c>
+      <c r="BN14" s="85">
         <v>0.85280286542244177</v>
       </c>
       <c r="BO14" s="27">
@@ -12269,10 +12290,10 @@
         <v>1.0192943828752512</v>
       </c>
       <c r="CA14" s="27">
-        <v>3.8581818181818184</v>
+        <v>3.8989898989898988</v>
       </c>
       <c r="CB14" s="26">
-        <v>0.53988214202057783</v>
+        <v>0.67621825170413041</v>
       </c>
       <c r="CC14" s="27">
         <v>2.9545454545454541</v>
@@ -12691,10 +12712,10 @@
       <c r="BL15" s="26">
         <v>0.63245553203367588</v>
       </c>
-      <c r="BM15" s="27">
-        <v>2.8666666666666663</v>
-      </c>
-      <c r="BN15" s="26">
+      <c r="BM15" s="84">
+        <v>3.1333333333333337</v>
+      </c>
+      <c r="BN15" s="85">
         <v>1.0600988273786194</v>
       </c>
       <c r="BO15" s="27">
@@ -12734,10 +12755,10 @@
         <v>0.91547541643412689</v>
       </c>
       <c r="CA15" s="27">
-        <v>3.6593333333333335</v>
+        <v>3.6888888888888891</v>
       </c>
       <c r="CB15" s="26">
-        <v>0.53566336265908476</v>
+        <v>0.61319989346659431</v>
       </c>
       <c r="CC15" s="27">
         <v>2.5333333333333337</v>
@@ -13156,10 +13177,10 @@
       <c r="BL16" s="26">
         <v>0.89294371874630751</v>
       </c>
-      <c r="BM16" s="27">
-        <v>2.7878787878787881</v>
-      </c>
-      <c r="BN16" s="26">
+      <c r="BM16" s="84">
+        <v>3.2121212121212119</v>
+      </c>
+      <c r="BN16" s="85">
         <v>1.1390120652778375</v>
       </c>
       <c r="BO16" s="27">
@@ -13199,10 +13220,10 @@
         <v>1.2439246298906073</v>
       </c>
       <c r="CA16" s="27">
-        <v>3.812121212121212</v>
+        <v>3.8585858585858581</v>
       </c>
       <c r="CB16" s="26">
-        <v>0.65263292504169956</v>
+        <v>0.81662543701326396</v>
       </c>
       <c r="CC16" s="27">
         <v>3.0303030303030303</v>
@@ -13621,10 +13642,10 @@
       <c r="BL17" s="26">
         <v>0.91387353346337541</v>
       </c>
-      <c r="BM17" s="27">
-        <v>2.6428571428571428</v>
-      </c>
-      <c r="BN17" s="26">
+      <c r="BM17" s="84">
+        <v>3.3571428571428572</v>
+      </c>
+      <c r="BN17" s="85">
         <v>1.3363062095621219</v>
       </c>
       <c r="BO17" s="27">
@@ -13664,10 +13685,10 @@
         <v>1.5898026693500447</v>
       </c>
       <c r="CA17" s="27">
-        <v>3.96</v>
+        <v>4.0396825396825404</v>
       </c>
       <c r="CB17" s="26">
-        <v>0.73838701547046781</v>
+        <v>0.86792276151543968</v>
       </c>
       <c r="CC17" s="27">
         <v>3.2142857142857144</v>
@@ -14086,10 +14107,10 @@
       <c r="BL18" s="26">
         <v>0.44721359549995793</v>
       </c>
-      <c r="BM18" s="27">
+      <c r="BM18" s="84">
         <v>3</v>
       </c>
-      <c r="BN18" s="26">
+      <c r="BN18" s="85">
         <v>1.4142135623730949</v>
       </c>
       <c r="BO18" s="27">
@@ -14129,10 +14150,10 @@
         <v>1.3038404810405297</v>
       </c>
       <c r="CA18" s="27">
-        <v>4.1779999999999999</v>
+        <v>4.1777777777777771</v>
       </c>
       <c r="CB18" s="26">
-        <v>0.31987497557639599</v>
+        <v>0.44859176084858565</v>
       </c>
       <c r="CC18" s="27">
         <v>2.8</v>
@@ -14551,10 +14572,10 @@
       <c r="BL19" s="26">
         <v>1.1352924243950935</v>
       </c>
-      <c r="BM19" s="27">
-        <v>3.1</v>
-      </c>
-      <c r="BN19" s="26">
+      <c r="BM19" s="84">
+        <v>2.9</v>
+      </c>
+      <c r="BN19" s="85">
         <v>1.1972189997378648</v>
       </c>
       <c r="BO19" s="27">
@@ -14594,10 +14615,10 @@
         <v>0.81649658092772603</v>
       </c>
       <c r="CA19" s="27">
-        <v>3.59</v>
+        <v>3.5666666666666664</v>
       </c>
       <c r="CB19" s="26">
-        <v>0.71538645344860852</v>
+        <v>0.80029144211233705</v>
       </c>
       <c r="CC19" s="27">
         <v>3.3999999999999995</v>
@@ -15016,7 +15037,7 @@
       <c r="BL20" s="29">
         <v>0</v>
       </c>
-      <c r="BM20" s="27">
+      <c r="BM20" s="84">
         <v>3</v>
       </c>
       <c r="BN20" s="29">
@@ -15059,7 +15080,7 @@
         <v>0</v>
       </c>
       <c r="CA20" s="27">
-        <v>3.56</v>
+        <v>3.5555555555555554</v>
       </c>
       <c r="CB20" s="29">
         <v>0</v>
@@ -15481,10 +15502,10 @@
       <c r="BL21" s="26">
         <v>1.0801234497346432</v>
       </c>
-      <c r="BM21" s="27">
-        <v>3.3000000000000003</v>
-      </c>
-      <c r="BN21" s="26">
+      <c r="BM21" s="84">
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="BN21" s="85">
         <v>0.82327260234856459</v>
       </c>
       <c r="BO21" s="27">
@@ -15524,10 +15545,10 @@
         <v>0.99442892601175326</v>
       </c>
       <c r="CA21" s="27">
-        <v>3.6669999999999998</v>
+        <v>3.6</v>
       </c>
       <c r="CB21" s="26">
-        <v>0.76852022311279056</v>
+        <v>0.82850452810254438</v>
       </c>
       <c r="CC21" s="27">
         <v>3.5</v>
@@ -15946,10 +15967,10 @@
       <c r="BL22" s="26">
         <v>1.707825127659933</v>
       </c>
-      <c r="BM22" s="27">
-        <v>2.75</v>
-      </c>
-      <c r="BN22" s="26">
+      <c r="BM22" s="84">
+        <v>3.25</v>
+      </c>
+      <c r="BN22" s="85">
         <v>1.2583057392117916</v>
       </c>
       <c r="BO22" s="27">
@@ -15989,10 +16010,10 @@
         <v>1</v>
       </c>
       <c r="CA22" s="27">
-        <v>3.6399999999999997</v>
+        <v>3.6944444444444446</v>
       </c>
       <c r="CB22" s="26">
-        <v>0.77356318423254844</v>
+        <v>1.0198644305936566</v>
       </c>
       <c r="CC22" s="27">
         <v>3.25</v>
@@ -16411,10 +16432,10 @@
       <c r="BL23" s="26">
         <v>0.91612538131290422</v>
       </c>
-      <c r="BM23" s="27">
+      <c r="BM23" s="84">
         <v>3</v>
       </c>
-      <c r="BN23" s="26">
+      <c r="BN23" s="85">
         <v>1.5118578920369088</v>
       </c>
       <c r="BO23" s="27">
@@ -16457,7 +16478,7 @@
         <v>3.75</v>
       </c>
       <c r="CB23" s="26">
-        <v>0.60818230349601132</v>
+        <v>0.81595639126824604</v>
       </c>
       <c r="CC23" s="27">
         <v>3.25</v>
@@ -16876,10 +16897,10 @@
       <c r="BL24" s="26">
         <v>0.75162162351482731</v>
       </c>
-      <c r="BM24" s="27">
-        <v>2.8181818181818179</v>
-      </c>
-      <c r="BN24" s="26">
+      <c r="BM24" s="84">
+        <v>3.1818181818181821</v>
+      </c>
+      <c r="BN24" s="85">
         <v>0.85280286542244177</v>
       </c>
       <c r="BO24" s="27">
@@ -16919,10 +16940,10 @@
         <v>1.3516063875403324</v>
       </c>
       <c r="CA24" s="27">
-        <v>3.6927272727272729</v>
+        <v>3.7323232323232318</v>
       </c>
       <c r="CB24" s="26">
-        <v>0.67723655442492936</v>
+        <v>0.76801054742191655</v>
       </c>
       <c r="CC24" s="27">
         <v>3.2272727272727275</v>
@@ -17341,10 +17362,10 @@
       <c r="BL25" s="26">
         <v>0</v>
       </c>
-      <c r="BM25" s="27">
-        <v>3.4</v>
-      </c>
-      <c r="BN25" s="26">
+      <c r="BM25" s="84">
+        <v>2.6</v>
+      </c>
+      <c r="BN25" s="85">
         <v>1.1401754250991381</v>
       </c>
       <c r="BO25" s="27">
@@ -17384,10 +17405,10 @@
         <v>0.70710678118654757</v>
       </c>
       <c r="CA25" s="27">
-        <v>3.246</v>
+        <v>3.1555555555555554</v>
       </c>
       <c r="CB25" s="26">
-        <v>0.51169326749528377</v>
+        <v>0.69210717788433052</v>
       </c>
       <c r="CC25" s="27">
         <v>4.4000000000000004</v>
@@ -17806,10 +17827,10 @@
       <c r="BL26" s="26">
         <v>1.0836246694508316</v>
       </c>
-      <c r="BM26" s="27">
-        <v>2.9166666666666665</v>
-      </c>
-      <c r="BN26" s="26">
+      <c r="BM26" s="84">
+        <v>3.0833333333333335</v>
+      </c>
+      <c r="BN26" s="85">
         <v>1.164500152881315</v>
       </c>
       <c r="BO26" s="27">
@@ -17849,10 +17870,10 @@
         <v>0.93743686656109193</v>
       </c>
       <c r="CA26" s="27">
-        <v>3.8158333333333339</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="CB26" s="26">
-        <v>0.691131592960327</v>
+        <v>0.78352852357159342</v>
       </c>
       <c r="CC26" s="27">
         <v>2.9166666666666665</v>
@@ -18271,10 +18292,10 @@
       <c r="BL27" s="26">
         <v>0.44721359549995793</v>
       </c>
-      <c r="BM27" s="27">
-        <v>2.8</v>
-      </c>
-      <c r="BN27" s="26">
+      <c r="BM27" s="84">
+        <v>3.2</v>
+      </c>
+      <c r="BN27" s="85">
         <v>1.3038404810405297</v>
       </c>
       <c r="BO27" s="27">
@@ -18314,10 +18335,10 @@
         <v>0.54772255750516619</v>
       </c>
       <c r="CA27" s="27">
-        <v>3.6219999999999999</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="CB27" s="26">
-        <v>0.50071948234515518</v>
+        <v>0.67128033186636504</v>
       </c>
       <c r="CC27" s="27">
         <v>3.4</v>
@@ -18736,10 +18757,10 @@
       <c r="BL28" s="26">
         <v>0.54772255750516607</v>
       </c>
-      <c r="BM28" s="27">
-        <v>2.4</v>
-      </c>
-      <c r="BN28" s="26">
+      <c r="BM28" s="84">
+        <v>3.6</v>
+      </c>
+      <c r="BN28" s="85">
         <v>0.89442719099991586</v>
       </c>
       <c r="BO28" s="27">
@@ -18779,10 +18800,10 @@
         <v>0.99999999999999989</v>
       </c>
       <c r="CA28" s="27">
-        <v>3.7540000000000004</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="CB28" s="26">
-        <v>0.59378447268348145</v>
+        <v>0.78173595997057166</v>
       </c>
       <c r="CC28" s="27">
         <v>3.2</v>
@@ -19201,10 +19222,10 @@
       <c r="BL29" s="26">
         <v>1.4142135623730951</v>
       </c>
-      <c r="BM29" s="27">
-        <v>2.5</v>
-      </c>
-      <c r="BN29" s="26">
+      <c r="BM29" s="84">
+        <v>3.5</v>
+      </c>
+      <c r="BN29" s="85">
         <v>2.1213203435596424</v>
       </c>
       <c r="BO29" s="27">
@@ -19244,10 +19265,10 @@
         <v>0.70710678118654757</v>
       </c>
       <c r="CA29" s="27">
-        <v>3.9400000000000004</v>
+        <v>4.0555555555555554</v>
       </c>
       <c r="CB29" s="26">
-        <v>0.70710678118654779</v>
+        <v>1.1785113019775795</v>
       </c>
       <c r="CC29" s="27">
         <v>4.5</v>
@@ -19666,10 +19687,10 @@
       <c r="BL30" s="26">
         <v>0.7559289460184544</v>
       </c>
-      <c r="BM30" s="27">
-        <v>3.0000000000000004</v>
-      </c>
-      <c r="BN30" s="26">
+      <c r="BM30" s="84">
+        <v>2.9999999999999996</v>
+      </c>
+      <c r="BN30" s="85">
         <v>1.0690449676496976</v>
       </c>
       <c r="BO30" s="27">
@@ -19712,7 +19733,7 @@
         <v>4.25</v>
       </c>
       <c r="CB30" s="26">
-        <v>0.57745748142797737</v>
+        <v>0.73162378898358804</v>
       </c>
       <c r="CC30" s="27">
         <v>3.125</v>
@@ -20131,10 +20152,10 @@
       <c r="BL31" s="26">
         <v>0.92680869599629834</v>
       </c>
-      <c r="BM31" s="27">
-        <v>3.3846153846153846</v>
-      </c>
-      <c r="BN31" s="26">
+      <c r="BM31" s="84">
+        <v>2.6153846153846154</v>
+      </c>
+      <c r="BN31" s="85">
         <v>1.0439078454267836</v>
       </c>
       <c r="BO31" s="27">
@@ -20174,10 +20195,10 @@
         <v>0.96741792204684496</v>
       </c>
       <c r="CA31" s="27">
-        <v>3.7361538461538459</v>
+        <v>3.6495726495726495</v>
       </c>
       <c r="CB31" s="26">
-        <v>0.59628766074687012</v>
+        <v>0.70978776438125313</v>
       </c>
       <c r="CC31" s="27">
         <v>3.1538461538461542</v>
@@ -20596,10 +20617,10 @@
       <c r="BL32" s="26">
         <v>0.752772652709081</v>
       </c>
-      <c r="BM32" s="27">
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="BN32" s="26">
+      <c r="BM32" s="84">
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="BN32" s="85">
         <v>0.5163977794943222</v>
       </c>
       <c r="BO32" s="27">
@@ -20639,10 +20660,10 @@
         <v>1.3784048752090221</v>
       </c>
       <c r="CA32" s="27">
-        <v>3.6466666666666669</v>
+        <v>3.574074074074074</v>
       </c>
       <c r="CB32" s="26">
-        <v>0.76505337504429516</v>
+        <v>0.74507988358417676</v>
       </c>
       <c r="CC32" s="27">
         <v>2.3333333333333335</v>
@@ -21061,10 +21082,10 @@
       <c r="BL33" s="26">
         <v>0.83845386974128566</v>
       </c>
-      <c r="BM33" s="27">
-        <v>3.1851851851851851</v>
-      </c>
-      <c r="BN33" s="26">
+      <c r="BM33" s="84">
+        <v>2.8148148148148149</v>
+      </c>
+      <c r="BN33" s="85">
         <v>1.0474420607937114</v>
       </c>
       <c r="BO33" s="27">
@@ -21104,10 +21125,10 @@
         <v>1.0093898773656798</v>
       </c>
       <c r="CA33" s="27">
-        <v>3.9596296296296307</v>
+        <v>3.9176954732510292</v>
       </c>
       <c r="CB33" s="26">
-        <v>0.58513008701327462</v>
+        <v>0.65260687273797024</v>
       </c>
       <c r="CC33" s="27">
         <v>3.1111111111111112</v>
@@ -21526,10 +21547,10 @@
       <c r="BL34" s="26">
         <v>0.9759000729485332</v>
       </c>
-      <c r="BM34" s="27">
-        <v>2.4285714285714288</v>
-      </c>
-      <c r="BN34" s="26">
+      <c r="BM34" s="84">
+        <v>3.5714285714285712</v>
+      </c>
+      <c r="BN34" s="85">
         <v>0.97590007294853331</v>
       </c>
       <c r="BO34" s="27">
@@ -21569,10 +21590,10 @@
         <v>1.1547005383792515</v>
       </c>
       <c r="CA34" s="27">
-        <v>3.4771428571428573</v>
+        <v>3.6031746031746033</v>
       </c>
       <c r="CB34" s="26">
-        <v>0.41503872452717328</v>
+        <v>0.56239180159988156</v>
       </c>
       <c r="CC34" s="27">
         <v>2.8571428571428568</v>
@@ -21991,10 +22012,10 @@
       <c r="BL35" s="26">
         <v>0.66666666666666663</v>
       </c>
-      <c r="BM35" s="27">
-        <v>2.8</v>
-      </c>
-      <c r="BN35" s="26">
+      <c r="BM35" s="84">
+        <v>3.2</v>
+      </c>
+      <c r="BN35" s="85">
         <v>0.78881063774661553</v>
       </c>
       <c r="BO35" s="27">
@@ -22034,10 +22055,10 @@
         <v>1.0801234497346432</v>
       </c>
       <c r="CA35" s="27">
-        <v>3.9340000000000002</v>
+        <v>3.9777777777777774</v>
       </c>
       <c r="CB35" s="26">
-        <v>0.53281641616351616</v>
+        <v>0.4823354250696209</v>
       </c>
       <c r="CC35" s="27">
         <v>2.8</v>
@@ -22456,10 +22477,10 @@
       <c r="BL36" s="26">
         <v>0.99999999999999989</v>
       </c>
-      <c r="BM36" s="27">
-        <v>4</v>
-      </c>
-      <c r="BN36" s="26">
+      <c r="BM36" s="84">
+        <v>2</v>
+      </c>
+      <c r="BN36" s="85">
         <v>1.1547005383792515</v>
       </c>
       <c r="BO36" s="27">
@@ -22499,10 +22520,10 @@
         <v>1.2909944487358056</v>
       </c>
       <c r="CA36" s="27">
-        <v>3.8624999999999998</v>
+        <v>3.6388888888888888</v>
       </c>
       <c r="CB36" s="26">
-        <v>0.68839789850541155</v>
+        <v>0.53958526979012822</v>
       </c>
       <c r="CC36" s="27">
         <v>3.25</v>
@@ -22921,10 +22942,10 @@
       <c r="BL37" s="26">
         <v>0.83214969703748021</v>
       </c>
-      <c r="BM37" s="27">
-        <v>3.032258064516129</v>
-      </c>
-      <c r="BN37" s="26">
+      <c r="BM37" s="84">
+        <v>2.967741935483871</v>
+      </c>
+      <c r="BN37" s="85">
         <v>1.0160010160015238</v>
       </c>
       <c r="BO37" s="27">
@@ -22964,10 +22985,10 @@
         <v>0.91228179008249899</v>
       </c>
       <c r="CA37" s="27">
-        <v>3.8864516129032256</v>
+        <v>3.8781362007168458</v>
       </c>
       <c r="CB37" s="26">
-        <v>0.54063264414385703</v>
+        <v>0.603388810429208</v>
       </c>
       <c r="CC37" s="27">
         <v>3.2580645161290325</v>
@@ -23386,10 +23407,10 @@
       <c r="BL38" s="26">
         <v>0.56713087281560048</v>
       </c>
-      <c r="BM38" s="27">
-        <v>3.3684210526315783</v>
-      </c>
-      <c r="BN38" s="26">
+      <c r="BM38" s="84">
+        <v>2.6315789473684217</v>
+      </c>
+      <c r="BN38" s="85">
         <v>0.76088591025268215</v>
       </c>
       <c r="BO38" s="27">
@@ -23429,10 +23450,10 @@
         <v>0.84811452387872421</v>
       </c>
       <c r="CA38" s="27">
-        <v>3.432631578947368</v>
+        <v>3.3508771929824559</v>
       </c>
       <c r="CB38" s="26">
-        <v>0.37079257611624872</v>
+        <v>0.39763215124279239</v>
       </c>
       <c r="CC38" s="27">
         <v>3.0526315789473681</v>
@@ -23851,10 +23872,10 @@
       <c r="BL39" s="26">
         <v>0.88191710368819676</v>
       </c>
-      <c r="BM39" s="27">
-        <v>2.6666666666666665</v>
-      </c>
-      <c r="BN39" s="26">
+      <c r="BM39" s="84">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="BN39" s="85">
         <v>0.70710678118654757</v>
       </c>
       <c r="BO39" s="27">
@@ -23894,10 +23915,10 @@
         <v>0.49999999999999989</v>
       </c>
       <c r="CA39" s="27">
-        <v>3.8144444444444439</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="CB39" s="26">
-        <v>0.51322780300542736</v>
+        <v>0.52411006289203366</v>
       </c>
       <c r="CC39" s="27">
         <v>3.2222222222222223</v>
@@ -24316,10 +24337,10 @@
       <c r="BL40" s="26">
         <v>0.53452248382484879</v>
       </c>
-      <c r="BM40" s="27">
-        <v>3.875</v>
-      </c>
-      <c r="BN40" s="26">
+      <c r="BM40" s="84">
+        <v>2.125</v>
+      </c>
+      <c r="BN40" s="85">
         <v>0.83452296039628016</v>
       </c>
       <c r="BO40" s="27">
@@ -24359,10 +24380,10 @@
         <v>0.91612538131290433</v>
       </c>
       <c r="CA40" s="27">
-        <v>3.5425000000000004</v>
+        <v>3.3472222222222223</v>
       </c>
       <c r="CB40" s="26">
-        <v>0.52215897962210689</v>
+        <v>0.45788217333292702</v>
       </c>
       <c r="CC40" s="27">
         <v>3.625</v>
@@ -24781,10 +24802,10 @@
       <c r="BL41" s="26">
         <v>1.1005049346146119</v>
       </c>
-      <c r="BM41" s="27">
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="BN41" s="26">
+      <c r="BM41" s="84">
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="BN41" s="85">
         <v>0.96609178307929577</v>
       </c>
       <c r="BO41" s="27">
@@ -24824,10 +24845,10 @@
         <v>1.1595018087284057</v>
       </c>
       <c r="CA41" s="27">
-        <v>3.7570000000000006</v>
+        <v>3.6222222222222218</v>
       </c>
       <c r="CB41" s="26">
-        <v>0.59552124693881014</v>
+        <v>0.70116501133032505</v>
       </c>
       <c r="CC41" s="27">
         <v>3.1</v>
@@ -25246,10 +25267,10 @@
       <c r="BL42" s="26">
         <v>0.89442719099991586</v>
       </c>
-      <c r="BM42" s="27">
-        <v>4</v>
-      </c>
-      <c r="BN42" s="26">
+      <c r="BM42" s="84">
+        <v>2</v>
+      </c>
+      <c r="BN42" s="85">
         <v>0.70710678118654757</v>
       </c>
       <c r="BO42" s="27">
@@ -25289,10 +25310,10 @@
         <v>0.70710678118654757</v>
       </c>
       <c r="CA42" s="27">
-        <v>3.7119999999999997</v>
+        <v>3.4888888888888885</v>
       </c>
       <c r="CB42" s="26">
-        <v>0.38035509724466671</v>
+        <v>0.2897423291201176</v>
       </c>
       <c r="CC42" s="27">
         <v>3.6</v>
@@ -25711,10 +25732,10 @@
       <c r="BL43" s="26">
         <v>0.76729693648846842</v>
       </c>
-      <c r="BM43" s="27">
-        <v>2.954545454545455</v>
-      </c>
-      <c r="BN43" s="26">
+      <c r="BM43" s="84">
+        <v>3.045454545454545</v>
+      </c>
+      <c r="BN43" s="85">
         <v>0.95005126314183819</v>
       </c>
       <c r="BO43" s="27">
@@ -25754,10 +25775,10 @@
         <v>1.1509454047327026</v>
       </c>
       <c r="CA43" s="27">
-        <v>3.5463636363636364</v>
+        <v>3.5555555555555554</v>
       </c>
       <c r="CB43" s="26">
-        <v>0.58768752188269524</v>
+        <v>0.65689487435610305</v>
       </c>
       <c r="CC43" s="27">
         <v>2.8181818181818183</v>
@@ -26176,10 +26197,10 @@
       <c r="BL44" s="26">
         <v>0.63245553203367577</v>
       </c>
-      <c r="BM44" s="27">
-        <v>2.8181818181818179</v>
-      </c>
-      <c r="BN44" s="26">
+      <c r="BM44" s="84">
+        <v>3.1818181818181821</v>
+      </c>
+      <c r="BN44" s="85">
         <v>0.98164981721404276</v>
       </c>
       <c r="BO44" s="27">
@@ -26219,10 +26240,10 @@
         <v>0.83120941459363362</v>
       </c>
       <c r="CA44" s="27">
-        <v>4.0999999999999996</v>
+        <v>4.1414141414141419</v>
       </c>
       <c r="CB44" s="26">
-        <v>0.47673892226248965</v>
+        <v>0.59231896039359655</v>
       </c>
       <c r="CC44" s="27">
         <v>3.4545454545454546</v>
@@ -26641,10 +26662,10 @@
       <c r="BL45" s="26">
         <v>0.96741792204684507</v>
       </c>
-      <c r="BM45" s="27">
-        <v>3.4615384615384617</v>
-      </c>
-      <c r="BN45" s="26">
+      <c r="BM45" s="84">
+        <v>2.5384615384615383</v>
+      </c>
+      <c r="BN45" s="85">
         <v>1.1266014242982161</v>
       </c>
       <c r="BO45" s="27">
@@ -26684,10 +26705,10 @@
         <v>1.0681880176381129</v>
       </c>
       <c r="CA45" s="27">
-        <v>3.8207692307692311</v>
+        <v>3.7179487179487181</v>
       </c>
       <c r="CB45" s="26">
-        <v>0.64707626467650037</v>
+        <v>0.79558372676092348</v>
       </c>
       <c r="CC45" s="27">
         <v>3.3076923076923075</v>
@@ -27106,10 +27127,10 @@
       <c r="BL46" s="26">
         <v>0.83333333333333326</v>
       </c>
-      <c r="BM46" s="27">
-        <v>1.8888888888888888</v>
-      </c>
-      <c r="BN46" s="26">
+      <c r="BM46" s="84">
+        <v>4.1111111111111107</v>
+      </c>
+      <c r="BN46" s="85">
         <v>1.2692955176439846</v>
       </c>
       <c r="BO46" s="27">
@@ -27149,10 +27170,10 @@
         <v>1.3017082793177757</v>
       </c>
       <c r="CA46" s="27">
-        <v>4.137777777777778</v>
+        <v>4.382716049382716</v>
       </c>
       <c r="CB46" s="26">
-        <v>0.41490293376215631</v>
+        <v>0.53028966901023544</v>
       </c>
       <c r="CC46" s="27">
         <v>4.333333333333333</v>
@@ -27571,10 +27592,10 @@
       <c r="BL47" s="26">
         <v>0.88640526042791834</v>
       </c>
-      <c r="BM47" s="27">
-        <v>1.5</v>
-      </c>
-      <c r="BN47" s="26">
+      <c r="BM47" s="84">
+        <v>4.5</v>
+      </c>
+      <c r="BN47" s="85">
         <v>0.7559289460184544</v>
       </c>
       <c r="BO47" s="27">
@@ -27614,10 +27635,10 @@
         <v>1.0350983390135313</v>
       </c>
       <c r="CA47" s="27">
-        <v>3.9724999999999997</v>
+        <v>4.3055555555555554</v>
       </c>
       <c r="CB47" s="26">
-        <v>0.5121035051627747</v>
+        <v>0.6164986186012209</v>
       </c>
       <c r="CC47" s="27">
         <v>4.875</v>
@@ -28036,11 +28057,11 @@
       <c r="BL48" s="26">
         <v>0.79707442270319728</v>
       </c>
-      <c r="BM48" s="27">
-        <v>2.2222222222222219</v>
-      </c>
-      <c r="BN48" s="26">
-        <v>1.3107054276032879</v>
+      <c r="BM48" s="84">
+        <v>3.7777777777777772</v>
+      </c>
+      <c r="BN48" s="85">
+        <v>1.3107054276032875</v>
       </c>
       <c r="BO48" s="27">
         <v>4.2962962962962967</v>
@@ -28079,10 +28100,10 @@
         <v>0.87705801930702931</v>
       </c>
       <c r="CA48" s="27">
-        <v>4.206666666666667</v>
+        <v>4.378600823045268</v>
       </c>
       <c r="CB48" s="26">
-        <v>0.51622892953834709</v>
+        <v>0.54017975557899089</v>
       </c>
       <c r="CC48" s="27">
         <v>4.1111111111111116</v>
@@ -28501,10 +28522,10 @@
       <c r="BL49" s="26">
         <v>0.59673910628985094</v>
       </c>
-      <c r="BM49" s="27">
-        <v>1.9024390243902445</v>
-      </c>
-      <c r="BN49" s="26">
+      <c r="BM49" s="84">
+        <v>4.0975609756097562</v>
+      </c>
+      <c r="BN49" s="85">
         <v>1.300093805246</v>
       </c>
       <c r="BO49" s="27">
@@ -28544,10 +28565,10 @@
         <v>1.1092735482639295</v>
       </c>
       <c r="CA49" s="27">
-        <v>4.2475609756097574</v>
+        <v>4.4905149051490501</v>
       </c>
       <c r="CB49" s="26">
-        <v>0.431866764684462</v>
+        <v>0.55886547872116166</v>
       </c>
       <c r="CC49" s="27">
         <v>4.4878048780487809</v>
@@ -28966,8 +28987,8 @@
       <c r="BL50" s="29">
         <v>0</v>
       </c>
-      <c r="BM50" s="27">
-        <v>1</v>
+      <c r="BM50" s="84">
+        <v>5</v>
       </c>
       <c r="BN50" s="29">
         <v>0</v>
@@ -29009,7 +29030,7 @@
         <v>0</v>
       </c>
       <c r="CA50" s="27">
-        <v>3.67</v>
+        <v>4.1111111111111107</v>
       </c>
       <c r="CB50" s="29">
         <v>0</v>
@@ -29431,10 +29452,10 @@
       <c r="BL51" s="26">
         <v>0.92796072713833722</v>
       </c>
-      <c r="BM51" s="27">
-        <v>2.5555555555555554</v>
-      </c>
-      <c r="BN51" s="26">
+      <c r="BM51" s="84">
+        <v>3.4444444444444446</v>
+      </c>
+      <c r="BN51" s="85">
         <v>1.5898986690282426</v>
       </c>
       <c r="BO51" s="27">
@@ -29474,10 +29495,10 @@
         <v>1.4240006242195886</v>
       </c>
       <c r="CA51" s="27">
-        <v>3.6177777777777775</v>
+        <v>3.7160493827160495</v>
       </c>
       <c r="CB51" s="26">
-        <v>0.95121997689516802</v>
+        <v>1.0958833055935921</v>
       </c>
       <c r="CC51" s="27">
         <v>3.1111111111111112</v>
@@ -29896,10 +29917,10 @@
       <c r="BL52" s="32">
         <v>0.74322335295720665</v>
       </c>
-      <c r="BM52" s="33">
-        <v>1.5333333333333332</v>
-      </c>
-      <c r="BN52" s="32">
+      <c r="BM52" s="84">
+        <v>4.4666666666666668</v>
+      </c>
+      <c r="BN52" s="85">
         <v>0.74322335295720654</v>
       </c>
       <c r="BO52" s="33">
@@ -29939,10 +29960,10 @@
         <v>0.91547541643412689</v>
       </c>
       <c r="CA52" s="33">
-        <v>4.1720000000000006</v>
+        <v>4.4962962962962951</v>
       </c>
       <c r="CB52" s="32">
-        <v>0.50349067234940603</v>
+        <v>0.57100219248377804</v>
       </c>
       <c r="CC52" s="33">
         <v>3.8000000000000003</v>
@@ -30361,10 +30382,10 @@
       <c r="BL53" s="36">
         <v>0.87096135964821586</v>
       </c>
-      <c r="BM53" s="37">
-        <v>2.8461538461538454</v>
-      </c>
-      <c r="BN53" s="36">
+      <c r="BM53" s="86">
+        <v>3.1538461538461546</v>
+      </c>
+      <c r="BN53" s="87">
         <v>1.1534257325700927</v>
       </c>
       <c r="BO53" s="37">
@@ -30404,10 +30425,10 @@
         <v>1.0775265943270809</v>
       </c>
       <c r="CA53" s="37">
-        <v>3.8697217675941076</v>
+        <v>3.9034369885433704</v>
       </c>
       <c r="CB53" s="36">
-        <v>0.59515262225020638</v>
+        <v>0.70378635042468374</v>
       </c>
       <c r="CC53" s="37">
         <v>3.3371522094926349</v>

--- a/대시보드_구축_데이터.xlsx
+++ b/대시보드_구축_데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\dashboard_v2\dashboard_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D097E2C2-C7BC-4E7E-9479-1F6A9FED53C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4BD6E0-113F-426B-A768-2AF33AB0AB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3F0FD738-DFD1-4862-A6F4-1A909B15B620}"/>
+    <workbookView xWindow="8805" yWindow="960" windowWidth="16770" windowHeight="12735" activeTab="1" xr2:uid="{3F0FD738-DFD1-4862-A6F4-1A909B15B620}"/>
   </bookViews>
   <sheets>
     <sheet name="유형분류" sheetId="4" r:id="rId1"/>
@@ -894,7 +894,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1048,13 +1048,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="3" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1063,7 +1057,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1151,6 +1144,10 @@
     <xf numFmtId="178" fontId="3" fillId="3" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1474,1857 +1471,1857 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:11" ht="28.5">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="G1" s="63" t="s">
+      <c r="G1" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="H1" s="63" t="s">
+      <c r="H1" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="I1" s="63" t="s">
+      <c r="I1" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="J1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="63" t="s">
+      <c r="J1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="60" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="62" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F2" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="66" t="s">
+      <c r="G2" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="J2" s="66" t="s">
+      <c r="J2" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="K2" s="67" t="s">
+      <c r="K2" s="64" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="69">
-        <v>0</v>
-      </c>
-      <c r="C3" s="70">
-        <v>0</v>
-      </c>
-      <c r="D3" s="71">
+      <c r="B3" s="66">
+        <v>0</v>
+      </c>
+      <c r="C3" s="67">
+        <v>0</v>
+      </c>
+      <c r="D3" s="68">
         <v>2</v>
       </c>
-      <c r="E3" s="70">
+      <c r="E3" s="67">
         <v>0.33333333333333337</v>
       </c>
-      <c r="F3" s="71">
+      <c r="F3" s="68">
         <v>4</v>
       </c>
-      <c r="G3" s="70">
+      <c r="G3" s="67">
         <v>0.66666666666666674</v>
       </c>
-      <c r="H3" s="71">
-        <v>0</v>
-      </c>
-      <c r="I3" s="70">
-        <v>0</v>
-      </c>
-      <c r="J3" s="71">
+      <c r="H3" s="68">
+        <v>0</v>
+      </c>
+      <c r="I3" s="67">
+        <v>0</v>
+      </c>
+      <c r="J3" s="68">
         <v>6</v>
       </c>
-      <c r="K3" s="72">
+      <c r="K3" s="69">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="74">
-        <v>0</v>
-      </c>
-      <c r="C4" s="75">
+      <c r="B4" s="71">
+        <v>0</v>
+      </c>
+      <c r="C4" s="72">
         <v>0</v>
       </c>
       <c r="D4" s="3">
         <v>2</v>
       </c>
-      <c r="E4" s="75">
+      <c r="E4" s="72">
         <v>0.28571428571428575</v>
       </c>
       <c r="F4" s="3">
         <v>3</v>
       </c>
-      <c r="G4" s="75">
+      <c r="G4" s="72">
         <v>0.42857142857142855</v>
       </c>
       <c r="H4" s="3">
         <v>2</v>
       </c>
-      <c r="I4" s="75">
+      <c r="I4" s="72">
         <v>0.28571428571428575</v>
       </c>
       <c r="J4" s="3">
         <v>7</v>
       </c>
-      <c r="K4" s="76">
+      <c r="K4" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="74">
-        <v>0</v>
-      </c>
-      <c r="C5" s="75">
+      <c r="B5" s="71">
+        <v>0</v>
+      </c>
+      <c r="C5" s="72">
         <v>0</v>
       </c>
       <c r="D5" s="3">
         <v>5</v>
       </c>
-      <c r="E5" s="75">
+      <c r="E5" s="72">
         <v>0.33333333333333337</v>
       </c>
       <c r="F5" s="3">
         <v>8</v>
       </c>
-      <c r="G5" s="75">
+      <c r="G5" s="72">
         <v>0.53333333333333333</v>
       </c>
       <c r="H5" s="3">
         <v>2</v>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="72">
         <v>0.13333333333333333</v>
       </c>
       <c r="J5" s="3">
         <v>15</v>
       </c>
-      <c r="K5" s="76">
+      <c r="K5" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="74">
+      <c r="B6" s="71">
         <v>1</v>
       </c>
-      <c r="C6" s="75">
+      <c r="C6" s="72">
         <v>0.2</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
-      <c r="E6" s="75">
+      <c r="E6" s="72">
         <v>0.6</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="75">
+      <c r="G6" s="72">
         <v>0.2</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
       </c>
-      <c r="I6" s="75">
+      <c r="I6" s="72">
         <v>0</v>
       </c>
       <c r="J6" s="3">
         <v>5</v>
       </c>
-      <c r="K6" s="76">
+      <c r="K6" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="74">
+      <c r="B7" s="71">
         <v>1</v>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="72">
         <v>0.1</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="72">
         <v>0.3</v>
       </c>
       <c r="F7" s="3">
         <v>6</v>
       </c>
-      <c r="G7" s="75">
+      <c r="G7" s="72">
         <v>0.6</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="72">
         <v>0</v>
       </c>
       <c r="J7" s="3">
         <v>10</v>
       </c>
-      <c r="K7" s="76">
+      <c r="K7" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="74">
-        <v>0</v>
-      </c>
-      <c r="C8" s="75">
+      <c r="B8" s="71">
+        <v>0</v>
+      </c>
+      <c r="C8" s="72">
         <v>0</v>
       </c>
       <c r="D8" s="3">
         <v>8</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="72">
         <v>0.4705882352941177</v>
       </c>
       <c r="F8" s="3">
         <v>6</v>
       </c>
-      <c r="G8" s="75">
+      <c r="G8" s="72">
         <v>0.35294117647058826</v>
       </c>
       <c r="H8" s="3">
         <v>3</v>
       </c>
-      <c r="I8" s="75">
+      <c r="I8" s="72">
         <v>0.17647058823529413</v>
       </c>
       <c r="J8" s="3">
         <v>17</v>
       </c>
-      <c r="K8" s="76">
+      <c r="K8" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="74">
-        <v>0</v>
-      </c>
-      <c r="C9" s="75">
+      <c r="B9" s="71">
+        <v>0</v>
+      </c>
+      <c r="C9" s="72">
         <v>0</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="72">
         <v>0.6</v>
       </c>
       <c r="F9" s="3">
         <v>2</v>
       </c>
-      <c r="G9" s="75">
+      <c r="G9" s="72">
         <v>0.4</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="72">
         <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>5</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="74">
-        <v>0</v>
-      </c>
-      <c r="C10" s="75">
+      <c r="B10" s="71">
+        <v>0</v>
+      </c>
+      <c r="C10" s="72">
         <v>0</v>
       </c>
       <c r="D10" s="3">
         <v>4</v>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="72">
         <v>0.4</v>
       </c>
       <c r="F10" s="3">
         <v>6</v>
       </c>
-      <c r="G10" s="75">
+      <c r="G10" s="72">
         <v>0.6</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="75">
+      <c r="I10" s="72">
         <v>0</v>
       </c>
       <c r="J10" s="3">
         <v>10</v>
       </c>
-      <c r="K10" s="76">
+      <c r="K10" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="74">
-        <v>0</v>
-      </c>
-      <c r="C11" s="75">
+      <c r="B11" s="71">
+        <v>0</v>
+      </c>
+      <c r="C11" s="72">
         <v>0</v>
       </c>
       <c r="D11" s="3">
         <v>8</v>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="72">
         <v>0.72727272727272729</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
       </c>
-      <c r="G11" s="75">
+      <c r="G11" s="72">
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="H11" s="3">
         <v>2</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="72">
         <v>0.18181818181818182</v>
       </c>
       <c r="J11" s="3">
         <v>11</v>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="74">
+      <c r="B12" s="71">
         <v>1</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="72">
         <v>0.1111111111111111</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="72">
         <v>0.33333333333333337</v>
       </c>
       <c r="F12" s="3">
         <v>5</v>
       </c>
-      <c r="G12" s="75">
+      <c r="G12" s="72">
         <v>0.55555555555555558</v>
       </c>
       <c r="H12" s="3">
         <v>0</v>
       </c>
-      <c r="I12" s="75">
+      <c r="I12" s="72">
         <v>0</v>
       </c>
       <c r="J12" s="3">
         <v>9</v>
       </c>
-      <c r="K12" s="76">
+      <c r="K12" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="74">
-        <v>0</v>
-      </c>
-      <c r="C13" s="75">
+      <c r="B13" s="71">
+        <v>0</v>
+      </c>
+      <c r="C13" s="72">
         <v>0</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="72">
         <v>0.66666666666666674</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="72">
         <v>0.33333333333333337</v>
       </c>
       <c r="H13" s="3">
         <v>0</v>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="72">
         <v>0</v>
       </c>
       <c r="J13" s="3">
         <v>3</v>
       </c>
-      <c r="K13" s="76">
+      <c r="K13" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="74">
+      <c r="B14" s="71">
         <v>4</v>
       </c>
-      <c r="C14" s="75">
+      <c r="C14" s="72">
         <v>0.18181818181818182</v>
       </c>
       <c r="D14" s="3">
         <v>7</v>
       </c>
-      <c r="E14" s="75">
+      <c r="E14" s="72">
         <v>0.31818181818181818</v>
       </c>
       <c r="F14" s="3">
         <v>10</v>
       </c>
-      <c r="G14" s="75">
+      <c r="G14" s="72">
         <v>0.45454545454545453</v>
       </c>
       <c r="H14" s="3">
         <v>1</v>
       </c>
-      <c r="I14" s="75">
+      <c r="I14" s="72">
         <v>4.5454545454545456E-2</v>
       </c>
       <c r="J14" s="3">
         <v>22</v>
       </c>
-      <c r="K14" s="76">
+      <c r="K14" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="74">
+      <c r="B15" s="71">
         <v>4</v>
       </c>
-      <c r="C15" s="75">
+      <c r="C15" s="72">
         <v>0.26666666666666666</v>
       </c>
       <c r="D15" s="3">
         <v>8</v>
       </c>
-      <c r="E15" s="75">
+      <c r="E15" s="72">
         <v>0.53333333333333333</v>
       </c>
       <c r="F15" s="3">
         <v>3</v>
       </c>
-      <c r="G15" s="75">
+      <c r="G15" s="72">
         <v>0.2</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
-      <c r="I15" s="75">
+      <c r="I15" s="72">
         <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>15</v>
       </c>
-      <c r="K15" s="76">
+      <c r="K15" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="73" t="s">
+      <c r="A16" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="74">
+      <c r="B16" s="71">
         <v>6</v>
       </c>
-      <c r="C16" s="75">
+      <c r="C16" s="72">
         <v>0.18181818181818182</v>
       </c>
       <c r="D16" s="3">
         <v>14</v>
       </c>
-      <c r="E16" s="75">
+      <c r="E16" s="72">
         <v>0.4242424242424242</v>
       </c>
       <c r="F16" s="3">
         <v>10</v>
       </c>
-      <c r="G16" s="75">
+      <c r="G16" s="72">
         <v>0.30303030303030304</v>
       </c>
       <c r="H16" s="3">
         <v>3</v>
       </c>
-      <c r="I16" s="75">
+      <c r="I16" s="72">
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="J16" s="3">
         <v>33</v>
       </c>
-      <c r="K16" s="76">
+      <c r="K16" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="74">
-        <v>0</v>
-      </c>
-      <c r="C17" s="75">
+      <c r="B17" s="71">
+        <v>0</v>
+      </c>
+      <c r="C17" s="72">
         <v>0</v>
       </c>
       <c r="D17" s="3">
         <v>2</v>
       </c>
-      <c r="E17" s="75">
+      <c r="E17" s="72">
         <v>0.14285714285714288</v>
       </c>
       <c r="F17" s="3">
         <v>7</v>
       </c>
-      <c r="G17" s="75">
+      <c r="G17" s="72">
         <v>0.5</v>
       </c>
       <c r="H17" s="3">
         <v>5</v>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="72">
         <v>0.35714285714285715</v>
       </c>
       <c r="J17" s="3">
         <v>14</v>
       </c>
-      <c r="K17" s="76">
+      <c r="K17" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="73" t="s">
+      <c r="A18" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="74">
-        <v>0</v>
-      </c>
-      <c r="C18" s="75">
+      <c r="B18" s="71">
+        <v>0</v>
+      </c>
+      <c r="C18" s="72">
         <v>0</v>
       </c>
       <c r="D18" s="3">
         <v>2</v>
       </c>
-      <c r="E18" s="75">
+      <c r="E18" s="72">
         <v>0.4</v>
       </c>
       <c r="F18" s="3">
         <v>3</v>
       </c>
-      <c r="G18" s="75">
+      <c r="G18" s="72">
         <v>0.6</v>
       </c>
       <c r="H18" s="3">
         <v>0</v>
       </c>
-      <c r="I18" s="75">
+      <c r="I18" s="72">
         <v>0</v>
       </c>
       <c r="J18" s="3">
         <v>5</v>
       </c>
-      <c r="K18" s="76">
+      <c r="K18" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="73" t="s">
+      <c r="A19" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="74">
+      <c r="B19" s="71">
         <v>2</v>
       </c>
-      <c r="C19" s="75">
+      <c r="C19" s="72">
         <v>0.2</v>
       </c>
       <c r="D19" s="3">
         <v>5</v>
       </c>
-      <c r="E19" s="75">
+      <c r="E19" s="72">
         <v>0.5</v>
       </c>
       <c r="F19" s="3">
         <v>3</v>
       </c>
-      <c r="G19" s="75">
+      <c r="G19" s="72">
         <v>0.3</v>
       </c>
       <c r="H19" s="3">
         <v>0</v>
       </c>
-      <c r="I19" s="75">
+      <c r="I19" s="72">
         <v>0</v>
       </c>
       <c r="J19" s="3">
         <v>10</v>
       </c>
-      <c r="K19" s="76">
+      <c r="K19" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="74">
-        <v>0</v>
-      </c>
-      <c r="C20" s="75">
+      <c r="B20" s="71">
+        <v>0</v>
+      </c>
+      <c r="C20" s="72">
         <v>0</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="72">
         <v>1</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="72">
         <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="75">
+      <c r="I20" s="72">
         <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>1</v>
       </c>
-      <c r="K20" s="76">
+      <c r="K20" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="74">
+      <c r="B21" s="71">
         <v>1</v>
       </c>
-      <c r="C21" s="75">
+      <c r="C21" s="72">
         <v>0.1</v>
       </c>
       <c r="D21" s="3">
         <v>4</v>
       </c>
-      <c r="E21" s="75">
+      <c r="E21" s="72">
         <v>0.4</v>
       </c>
       <c r="F21" s="3">
         <v>5</v>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="72">
         <v>0.5</v>
       </c>
       <c r="H21" s="3">
         <v>0</v>
       </c>
-      <c r="I21" s="75">
+      <c r="I21" s="72">
         <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>10</v>
       </c>
-      <c r="K21" s="76">
+      <c r="K21" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="73" t="s">
+      <c r="A22" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="74">
-        <v>0</v>
-      </c>
-      <c r="C22" s="75">
+      <c r="B22" s="71">
+        <v>0</v>
+      </c>
+      <c r="C22" s="72">
         <v>0</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="72">
         <v>0.25</v>
       </c>
       <c r="F22" s="3">
         <v>2</v>
       </c>
-      <c r="G22" s="75">
+      <c r="G22" s="72">
         <v>0.5</v>
       </c>
       <c r="H22" s="3">
         <v>1</v>
       </c>
-      <c r="I22" s="75">
+      <c r="I22" s="72">
         <v>0.25</v>
       </c>
       <c r="J22" s="3">
         <v>4</v>
       </c>
-      <c r="K22" s="76">
+      <c r="K22" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="74">
-        <v>0</v>
-      </c>
-      <c r="C23" s="75">
+      <c r="B23" s="71">
+        <v>0</v>
+      </c>
+      <c r="C23" s="72">
         <v>0</v>
       </c>
       <c r="D23" s="3">
         <v>4</v>
       </c>
-      <c r="E23" s="75">
+      <c r="E23" s="72">
         <v>0.5</v>
       </c>
       <c r="F23" s="3">
         <v>3</v>
       </c>
-      <c r="G23" s="75">
+      <c r="G23" s="72">
         <v>0.375</v>
       </c>
       <c r="H23" s="3">
         <v>1</v>
       </c>
-      <c r="I23" s="75">
+      <c r="I23" s="72">
         <v>0.125</v>
       </c>
       <c r="J23" s="3">
         <v>8</v>
       </c>
-      <c r="K23" s="76">
+      <c r="K23" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="74">
+      <c r="B24" s="71">
         <v>3</v>
       </c>
-      <c r="C24" s="75">
+      <c r="C24" s="72">
         <v>0.13636363636363635</v>
       </c>
       <c r="D24" s="3">
         <v>9</v>
       </c>
-      <c r="E24" s="75">
+      <c r="E24" s="72">
         <v>0.40909090909090906</v>
       </c>
       <c r="F24" s="3">
         <v>5</v>
       </c>
-      <c r="G24" s="75">
+      <c r="G24" s="72">
         <v>0.22727272727272727</v>
       </c>
       <c r="H24" s="3">
         <v>5</v>
       </c>
-      <c r="I24" s="75">
+      <c r="I24" s="72">
         <v>0.22727272727272727</v>
       </c>
       <c r="J24" s="3">
         <v>22</v>
       </c>
-      <c r="K24" s="76">
+      <c r="K24" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="74">
-        <v>0</v>
-      </c>
-      <c r="C25" s="75">
+      <c r="B25" s="71">
+        <v>0</v>
+      </c>
+      <c r="C25" s="72">
         <v>0</v>
       </c>
       <c r="D25" s="3">
         <v>5</v>
       </c>
-      <c r="E25" s="75">
+      <c r="E25" s="72">
         <v>1</v>
       </c>
       <c r="F25" s="3">
         <v>0</v>
       </c>
-      <c r="G25" s="75">
+      <c r="G25" s="72">
         <v>0</v>
       </c>
       <c r="H25" s="3">
         <v>0</v>
       </c>
-      <c r="I25" s="75">
+      <c r="I25" s="72">
         <v>0</v>
       </c>
       <c r="J25" s="3">
         <v>5</v>
       </c>
-      <c r="K25" s="76">
+      <c r="K25" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="73" t="s">
+      <c r="A26" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="74">
+      <c r="B26" s="71">
         <v>3</v>
       </c>
-      <c r="C26" s="75">
+      <c r="C26" s="72">
         <v>0.25</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
       </c>
-      <c r="E26" s="75">
+      <c r="E26" s="72">
         <v>0.16666666666666669</v>
       </c>
       <c r="F26" s="3">
         <v>6</v>
       </c>
-      <c r="G26" s="75">
+      <c r="G26" s="72">
         <v>0.5</v>
       </c>
       <c r="H26" s="3">
         <v>1</v>
       </c>
-      <c r="I26" s="75">
+      <c r="I26" s="72">
         <v>8.3333333333333343E-2</v>
       </c>
       <c r="J26" s="3">
         <v>12</v>
       </c>
-      <c r="K26" s="76">
+      <c r="K26" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="73" t="s">
+      <c r="A27" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="74">
+      <c r="B27" s="71">
         <v>2</v>
       </c>
-      <c r="C27" s="75">
+      <c r="C27" s="72">
         <v>0.4</v>
       </c>
       <c r="D27" s="3">
         <v>3</v>
       </c>
-      <c r="E27" s="75">
+      <c r="E27" s="72">
         <v>0.6</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
       </c>
-      <c r="G27" s="75">
+      <c r="G27" s="72">
         <v>0</v>
       </c>
       <c r="H27" s="3">
         <v>0</v>
       </c>
-      <c r="I27" s="75">
+      <c r="I27" s="72">
         <v>0</v>
       </c>
       <c r="J27" s="3">
         <v>5</v>
       </c>
-      <c r="K27" s="76">
+      <c r="K27" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="73" t="s">
+      <c r="A28" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="74">
-        <v>0</v>
-      </c>
-      <c r="C28" s="75">
+      <c r="B28" s="71">
+        <v>0</v>
+      </c>
+      <c r="C28" s="72">
         <v>0</v>
       </c>
       <c r="D28" s="3">
         <v>4</v>
       </c>
-      <c r="E28" s="75">
+      <c r="E28" s="72">
         <v>0.8</v>
       </c>
       <c r="F28" s="3">
         <v>1</v>
       </c>
-      <c r="G28" s="75">
+      <c r="G28" s="72">
         <v>0.2</v>
       </c>
       <c r="H28" s="3">
         <v>0</v>
       </c>
-      <c r="I28" s="75">
+      <c r="I28" s="72">
         <v>0</v>
       </c>
       <c r="J28" s="3">
         <v>5</v>
       </c>
-      <c r="K28" s="76">
+      <c r="K28" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="73" t="s">
+      <c r="A29" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="74">
+      <c r="B29" s="71">
         <v>1</v>
       </c>
-      <c r="C29" s="75">
+      <c r="C29" s="72">
         <v>0.5</v>
       </c>
       <c r="D29" s="3">
         <v>0</v>
       </c>
-      <c r="E29" s="75">
+      <c r="E29" s="72">
         <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
-      <c r="G29" s="75">
+      <c r="G29" s="72">
         <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>1</v>
       </c>
-      <c r="I29" s="75">
+      <c r="I29" s="72">
         <v>0.5</v>
       </c>
       <c r="J29" s="3">
         <v>2</v>
       </c>
-      <c r="K29" s="76">
+      <c r="K29" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="73" t="s">
+      <c r="A30" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="74">
-        <v>0</v>
-      </c>
-      <c r="C30" s="75">
+      <c r="B30" s="71">
+        <v>0</v>
+      </c>
+      <c r="C30" s="72">
         <v>0</v>
       </c>
       <c r="D30" s="3">
         <v>2</v>
       </c>
-      <c r="E30" s="75">
+      <c r="E30" s="72">
         <v>0.25</v>
       </c>
       <c r="F30" s="3">
         <v>5</v>
       </c>
-      <c r="G30" s="75">
+      <c r="G30" s="72">
         <v>0.625</v>
       </c>
       <c r="H30" s="3">
         <v>1</v>
       </c>
-      <c r="I30" s="75">
+      <c r="I30" s="72">
         <v>0.125</v>
       </c>
       <c r="J30" s="3">
         <v>8</v>
       </c>
-      <c r="K30" s="76">
+      <c r="K30" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="73" t="s">
+      <c r="A31" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="74">
+      <c r="B31" s="71">
         <v>2</v>
       </c>
-      <c r="C31" s="75">
+      <c r="C31" s="72">
         <v>0.15384615384615385</v>
       </c>
       <c r="D31" s="3">
         <v>5</v>
       </c>
-      <c r="E31" s="75">
+      <c r="E31" s="72">
         <v>0.38461538461538458</v>
       </c>
       <c r="F31" s="3">
         <v>5</v>
       </c>
-      <c r="G31" s="75">
+      <c r="G31" s="72">
         <v>0.38461538461538458</v>
       </c>
       <c r="H31" s="3">
         <v>1</v>
       </c>
-      <c r="I31" s="75">
+      <c r="I31" s="72">
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="J31" s="3">
         <v>13</v>
       </c>
-      <c r="K31" s="76">
+      <c r="K31" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="73" t="s">
+      <c r="A32" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="74">
+      <c r="B32" s="71">
         <v>1</v>
       </c>
-      <c r="C32" s="75">
+      <c r="C32" s="72">
         <v>0.16666666666666669</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
       </c>
-      <c r="E32" s="75">
+      <c r="E32" s="72">
         <v>0.16666666666666669</v>
       </c>
       <c r="F32" s="3">
         <v>4</v>
       </c>
-      <c r="G32" s="75">
+      <c r="G32" s="72">
         <v>0.66666666666666674</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="75">
+      <c r="I32" s="72">
         <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>6</v>
       </c>
-      <c r="K32" s="76">
+      <c r="K32" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="73" t="s">
+      <c r="A33" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="74">
+      <c r="B33" s="71">
         <v>7</v>
       </c>
-      <c r="C33" s="75">
+      <c r="C33" s="72">
         <v>0.12962962962962965</v>
       </c>
       <c r="D33" s="3">
         <v>18</v>
       </c>
-      <c r="E33" s="75">
+      <c r="E33" s="72">
         <v>0.33333333333333337</v>
       </c>
       <c r="F33" s="3">
         <v>17</v>
       </c>
-      <c r="G33" s="75">
+      <c r="G33" s="72">
         <v>0.31481481481481483</v>
       </c>
       <c r="H33" s="3">
         <v>12</v>
       </c>
-      <c r="I33" s="75">
+      <c r="I33" s="72">
         <v>0.22222222222222221</v>
       </c>
       <c r="J33" s="3">
         <v>54</v>
       </c>
-      <c r="K33" s="76">
+      <c r="K33" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="73" t="s">
+      <c r="A34" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="74">
+      <c r="B34" s="71">
         <v>2</v>
       </c>
-      <c r="C34" s="75">
+      <c r="C34" s="72">
         <v>0.28571428571428575</v>
       </c>
       <c r="D34" s="3">
         <v>4</v>
       </c>
-      <c r="E34" s="75">
+      <c r="E34" s="72">
         <v>0.57142857142857151</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
       </c>
-      <c r="G34" s="75">
+      <c r="G34" s="72">
         <v>0.14285714285714288</v>
       </c>
       <c r="H34" s="3">
         <v>0</v>
       </c>
-      <c r="I34" s="75">
+      <c r="I34" s="72">
         <v>0</v>
       </c>
       <c r="J34" s="3">
         <v>7</v>
       </c>
-      <c r="K34" s="76">
+      <c r="K34" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="74">
+      <c r="B35" s="71">
         <v>1</v>
       </c>
-      <c r="C35" s="75">
+      <c r="C35" s="72">
         <v>0.1</v>
       </c>
       <c r="D35" s="3">
         <v>2</v>
       </c>
-      <c r="E35" s="75">
+      <c r="E35" s="72">
         <v>0.2</v>
       </c>
       <c r="F35" s="3">
         <v>6</v>
       </c>
-      <c r="G35" s="75">
+      <c r="G35" s="72">
         <v>0.6</v>
       </c>
       <c r="H35" s="3">
         <v>1</v>
       </c>
-      <c r="I35" s="75">
+      <c r="I35" s="72">
         <v>0.1</v>
       </c>
       <c r="J35" s="3">
         <v>10</v>
       </c>
-      <c r="K35" s="76">
+      <c r="K35" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="73" t="s">
+      <c r="A36" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="74">
-        <v>0</v>
-      </c>
-      <c r="C36" s="75">
+      <c r="B36" s="71">
+        <v>0</v>
+      </c>
+      <c r="C36" s="72">
         <v>0</v>
       </c>
       <c r="D36" s="3">
         <v>2</v>
       </c>
-      <c r="E36" s="75">
+      <c r="E36" s="72">
         <v>0.5</v>
       </c>
       <c r="F36" s="3">
         <v>2</v>
       </c>
-      <c r="G36" s="75">
+      <c r="G36" s="72">
         <v>0.5</v>
       </c>
       <c r="H36" s="3">
         <v>0</v>
       </c>
-      <c r="I36" s="75">
+      <c r="I36" s="72">
         <v>0</v>
       </c>
       <c r="J36" s="3">
         <v>4</v>
       </c>
-      <c r="K36" s="76">
+      <c r="K36" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="74">
+      <c r="B37" s="71">
         <v>2</v>
       </c>
-      <c r="C37" s="75">
+      <c r="C37" s="72">
         <v>6.4516129032258063E-2</v>
       </c>
       <c r="D37" s="3">
         <v>12</v>
       </c>
-      <c r="E37" s="75">
+      <c r="E37" s="72">
         <v>0.38709677419354838</v>
       </c>
       <c r="F37" s="3">
         <v>11</v>
       </c>
-      <c r="G37" s="75">
+      <c r="G37" s="72">
         <v>0.35483870967741937</v>
       </c>
       <c r="H37" s="3">
         <v>6</v>
       </c>
-      <c r="I37" s="75">
+      <c r="I37" s="72">
         <v>0.19354838709677419</v>
       </c>
       <c r="J37" s="3">
         <v>31</v>
       </c>
-      <c r="K37" s="76">
+      <c r="K37" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="73" t="s">
+      <c r="A38" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="74">
+      <c r="B38" s="71">
         <v>7</v>
       </c>
-      <c r="C38" s="75">
+      <c r="C38" s="72">
         <v>0.36842105263157898</v>
       </c>
       <c r="D38" s="3">
         <v>9</v>
       </c>
-      <c r="E38" s="75">
+      <c r="E38" s="72">
         <v>0.47368421052631582</v>
       </c>
       <c r="F38" s="3">
         <v>3</v>
       </c>
-      <c r="G38" s="75">
+      <c r="G38" s="72">
         <v>0.15789473684210525</v>
       </c>
       <c r="H38" s="3">
         <v>0</v>
       </c>
-      <c r="I38" s="75">
+      <c r="I38" s="72">
         <v>0</v>
       </c>
       <c r="J38" s="3">
         <v>19</v>
       </c>
-      <c r="K38" s="76">
+      <c r="K38" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="74">
+      <c r="B39" s="71">
         <v>1</v>
       </c>
-      <c r="C39" s="75">
+      <c r="C39" s="72">
         <v>0.1111111111111111</v>
       </c>
       <c r="D39" s="3">
         <v>3</v>
       </c>
-      <c r="E39" s="75">
+      <c r="E39" s="72">
         <v>0.33333333333333337</v>
       </c>
       <c r="F39" s="3">
         <v>3</v>
       </c>
-      <c r="G39" s="75">
+      <c r="G39" s="72">
         <v>0.33333333333333337</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="75">
+      <c r="I39" s="72">
         <v>0.22222222222222221</v>
       </c>
       <c r="J39" s="3">
         <v>9</v>
       </c>
-      <c r="K39" s="76">
+      <c r="K39" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="74">
+      <c r="B40" s="71">
         <v>1</v>
       </c>
-      <c r="C40" s="75">
+      <c r="C40" s="72">
         <v>0.125</v>
       </c>
       <c r="D40" s="3">
         <v>4</v>
       </c>
-      <c r="E40" s="75">
+      <c r="E40" s="72">
         <v>0.5</v>
       </c>
       <c r="F40" s="3">
         <v>3</v>
       </c>
-      <c r="G40" s="75">
+      <c r="G40" s="72">
         <v>0.375</v>
       </c>
       <c r="H40" s="3">
         <v>0</v>
       </c>
-      <c r="I40" s="75">
+      <c r="I40" s="72">
         <v>0</v>
       </c>
       <c r="J40" s="3">
         <v>8</v>
       </c>
-      <c r="K40" s="76">
+      <c r="K40" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="73" t="s">
+      <c r="A41" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="74">
+      <c r="B41" s="71">
         <v>1</v>
       </c>
-      <c r="C41" s="75">
+      <c r="C41" s="72">
         <v>0.1</v>
       </c>
       <c r="D41" s="3">
         <v>4</v>
       </c>
-      <c r="E41" s="75">
+      <c r="E41" s="72">
         <v>0.4</v>
       </c>
       <c r="F41" s="3">
         <v>4</v>
       </c>
-      <c r="G41" s="75">
+      <c r="G41" s="72">
         <v>0.4</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="75">
+      <c r="I41" s="72">
         <v>0.1</v>
       </c>
       <c r="J41" s="3">
         <v>10</v>
       </c>
-      <c r="K41" s="76">
+      <c r="K41" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="74">
-        <v>0</v>
-      </c>
-      <c r="C42" s="75">
+      <c r="B42" s="71">
+        <v>0</v>
+      </c>
+      <c r="C42" s="72">
         <v>0</v>
       </c>
       <c r="D42" s="3">
         <v>5</v>
       </c>
-      <c r="E42" s="75">
+      <c r="E42" s="72">
         <v>1</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
-      <c r="G42" s="75">
+      <c r="G42" s="72">
         <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
-      <c r="I42" s="75">
+      <c r="I42" s="72">
         <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>5</v>
       </c>
-      <c r="K42" s="76">
+      <c r="K42" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="74">
+      <c r="B43" s="71">
         <v>7</v>
       </c>
-      <c r="C43" s="75">
+      <c r="C43" s="72">
         <v>0.31818181818181818</v>
       </c>
       <c r="D43" s="3">
         <v>8</v>
       </c>
-      <c r="E43" s="75">
+      <c r="E43" s="72">
         <v>0.36363636363636365</v>
       </c>
       <c r="F43" s="3">
         <v>7</v>
       </c>
-      <c r="G43" s="75">
+      <c r="G43" s="72">
         <v>0.31818181818181818</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
       </c>
-      <c r="I43" s="75">
+      <c r="I43" s="72">
         <v>0</v>
       </c>
       <c r="J43" s="3">
         <v>22</v>
       </c>
-      <c r="K43" s="76">
+      <c r="K43" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="74">
-        <v>0</v>
-      </c>
-      <c r="C44" s="75">
+      <c r="B44" s="71">
+        <v>0</v>
+      </c>
+      <c r="C44" s="72">
         <v>0</v>
       </c>
       <c r="D44" s="3">
         <v>4</v>
       </c>
-      <c r="E44" s="75">
+      <c r="E44" s="72">
         <v>0.36363636363636365</v>
       </c>
       <c r="F44" s="3">
         <v>7</v>
       </c>
-      <c r="G44" s="75">
+      <c r="G44" s="72">
         <v>0.63636363636363635</v>
       </c>
       <c r="H44" s="3">
         <v>0</v>
       </c>
-      <c r="I44" s="75">
+      <c r="I44" s="72">
         <v>0</v>
       </c>
       <c r="J44" s="3">
         <v>11</v>
       </c>
-      <c r="K44" s="76">
+      <c r="K44" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="73" t="s">
+      <c r="A45" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="74">
+      <c r="B45" s="71">
         <v>1</v>
       </c>
-      <c r="C45" s="75">
+      <c r="C45" s="72">
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="D45" s="3">
         <v>7</v>
       </c>
-      <c r="E45" s="75">
+      <c r="E45" s="72">
         <v>0.53846153846153844</v>
       </c>
       <c r="F45" s="3">
         <v>4</v>
       </c>
-      <c r="G45" s="75">
+      <c r="G45" s="72">
         <v>0.30769230769230771</v>
       </c>
       <c r="H45" s="3">
         <v>1</v>
       </c>
-      <c r="I45" s="75">
+      <c r="I45" s="72">
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="J45" s="3">
         <v>13</v>
       </c>
-      <c r="K45" s="76">
+      <c r="K45" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="73" t="s">
+      <c r="A46" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="74">
-        <v>0</v>
-      </c>
-      <c r="C46" s="75">
+      <c r="B46" s="71">
+        <v>0</v>
+      </c>
+      <c r="C46" s="72">
         <v>0</v>
       </c>
       <c r="D46" s="3">
         <v>3</v>
       </c>
-      <c r="E46" s="75">
+      <c r="E46" s="72">
         <v>0.33333333333333337</v>
       </c>
       <c r="F46" s="3">
         <v>2</v>
       </c>
-      <c r="G46" s="75">
+      <c r="G46" s="72">
         <v>0.22222222222222221</v>
       </c>
       <c r="H46" s="3">
         <v>4</v>
       </c>
-      <c r="I46" s="75">
+      <c r="I46" s="72">
         <v>0.44444444444444442</v>
       </c>
       <c r="J46" s="3">
         <v>9</v>
       </c>
-      <c r="K46" s="76">
+      <c r="K46" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="74">
-        <v>0</v>
-      </c>
-      <c r="C47" s="75">
+      <c r="B47" s="71">
+        <v>0</v>
+      </c>
+      <c r="C47" s="72">
         <v>0</v>
       </c>
       <c r="D47" s="3">
         <v>2</v>
       </c>
-      <c r="E47" s="75">
+      <c r="E47" s="72">
         <v>0.25</v>
       </c>
       <c r="F47" s="3">
         <v>4</v>
       </c>
-      <c r="G47" s="75">
+      <c r="G47" s="72">
         <v>0.5</v>
       </c>
       <c r="H47" s="3">
         <v>2</v>
       </c>
-      <c r="I47" s="75">
+      <c r="I47" s="72">
         <v>0.25</v>
       </c>
       <c r="J47" s="3">
         <v>8</v>
       </c>
-      <c r="K47" s="76">
+      <c r="K47" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="73" t="s">
+      <c r="A48" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="74">
+      <c r="B48" s="71">
         <v>1</v>
       </c>
-      <c r="C48" s="75">
+      <c r="C48" s="72">
         <v>3.7037037037037035E-2</v>
       </c>
       <c r="D48" s="3">
         <v>3</v>
       </c>
-      <c r="E48" s="75">
+      <c r="E48" s="72">
         <v>0.1111111111111111</v>
       </c>
       <c r="F48" s="3">
         <v>10</v>
       </c>
-      <c r="G48" s="75">
+      <c r="G48" s="72">
         <v>0.37037037037037041</v>
       </c>
       <c r="H48" s="3">
         <v>13</v>
       </c>
-      <c r="I48" s="75">
+      <c r="I48" s="72">
         <v>0.48148148148148145</v>
       </c>
       <c r="J48" s="3">
         <v>27</v>
       </c>
-      <c r="K48" s="76">
+      <c r="K48" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="73" t="s">
+      <c r="A49" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="74">
+      <c r="B49" s="71">
         <v>1</v>
       </c>
-      <c r="C49" s="75">
+      <c r="C49" s="72">
         <v>2.4390243902439025E-2</v>
       </c>
       <c r="D49" s="3">
         <v>5</v>
       </c>
-      <c r="E49" s="75">
+      <c r="E49" s="72">
         <v>0.12195121951219512</v>
       </c>
       <c r="F49" s="3">
         <v>16</v>
       </c>
-      <c r="G49" s="75">
+      <c r="G49" s="72">
         <v>0.3902439024390244</v>
       </c>
       <c r="H49" s="3">
         <v>19</v>
       </c>
-      <c r="I49" s="75">
+      <c r="I49" s="72">
         <v>0.46341463414634149</v>
       </c>
       <c r="J49" s="3">
         <v>41</v>
       </c>
-      <c r="K49" s="76">
+      <c r="K49" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="73" t="s">
+      <c r="A50" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="74">
-        <v>0</v>
-      </c>
-      <c r="C50" s="75">
+      <c r="B50" s="71">
+        <v>0</v>
+      </c>
+      <c r="C50" s="72">
         <v>0</v>
       </c>
       <c r="D50" s="3">
         <v>0</v>
       </c>
-      <c r="E50" s="75">
+      <c r="E50" s="72">
         <v>0</v>
       </c>
       <c r="F50" s="3">
         <v>1</v>
       </c>
-      <c r="G50" s="75">
+      <c r="G50" s="72">
         <v>1</v>
       </c>
       <c r="H50" s="3">
         <v>0</v>
       </c>
-      <c r="I50" s="75">
+      <c r="I50" s="72">
         <v>0</v>
       </c>
       <c r="J50" s="3">
         <v>1</v>
       </c>
-      <c r="K50" s="76">
+      <c r="K50" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="73" t="s">
+      <c r="A51" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="74">
+      <c r="B51" s="71">
         <v>4</v>
       </c>
-      <c r="C51" s="75">
+      <c r="C51" s="72">
         <v>0.44444444444444442</v>
       </c>
       <c r="D51" s="3">
         <v>2</v>
       </c>
-      <c r="E51" s="75">
+      <c r="E51" s="72">
         <v>0.22222222222222221</v>
       </c>
       <c r="F51" s="3">
         <v>1</v>
       </c>
-      <c r="G51" s="75">
+      <c r="G51" s="72">
         <v>0.1111111111111111</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="75">
+      <c r="I51" s="72">
         <v>0.22222222222222221</v>
       </c>
       <c r="J51" s="3">
         <v>9</v>
       </c>
-      <c r="K51" s="76">
+      <c r="K51" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="73" t="s">
+      <c r="A52" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="74">
-        <v>0</v>
-      </c>
-      <c r="C52" s="75">
+      <c r="B52" s="71">
+        <v>0</v>
+      </c>
+      <c r="C52" s="72">
         <v>0</v>
       </c>
       <c r="D52" s="3">
         <v>3</v>
       </c>
-      <c r="E52" s="75">
+      <c r="E52" s="72">
         <v>0.2</v>
       </c>
       <c r="F52" s="3">
         <v>4</v>
       </c>
-      <c r="G52" s="75">
+      <c r="G52" s="72">
         <v>0.26666666666666666</v>
       </c>
       <c r="H52" s="3">
         <v>8</v>
       </c>
-      <c r="I52" s="75">
+      <c r="I52" s="72">
         <v>0.53333333333333333</v>
       </c>
       <c r="J52" s="3">
         <v>15</v>
       </c>
-      <c r="K52" s="76">
+      <c r="K52" s="73">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" s="78">
+      <c r="A53" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="75">
         <v>68</v>
       </c>
-      <c r="C53" s="79">
+      <c r="C53" s="76">
         <v>0.11129296235679215</v>
       </c>
-      <c r="D53" s="80">
+      <c r="D53" s="77">
         <v>222</v>
       </c>
-      <c r="E53" s="79">
+      <c r="E53" s="76">
         <v>0.36333878887070375</v>
       </c>
-      <c r="F53" s="80">
+      <c r="F53" s="77">
         <v>221</v>
       </c>
-      <c r="G53" s="79">
+      <c r="G53" s="76">
         <v>0.36170212765957444</v>
       </c>
-      <c r="H53" s="80">
+      <c r="H53" s="77">
         <v>100</v>
       </c>
-      <c r="I53" s="79">
+      <c r="I53" s="76">
         <v>0.16366612111292964</v>
       </c>
-      <c r="J53" s="80">
+      <c r="J53" s="77">
         <v>611</v>
       </c>
-      <c r="K53" s="81">
+      <c r="K53" s="78">
         <v>1</v>
       </c>
     </row>
@@ -3350,46 +3347,46 @@
       <c r="B1" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="G1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="60" t="s">
+      <c r="I1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="60" t="s">
+      <c r="J1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="60" t="s">
+      <c r="K1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="60" t="s">
+      <c r="L1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="60" t="s">
+      <c r="M1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="60" t="s">
+      <c r="N1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="59" t="s">
+      <c r="O1" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="59" t="s">
+      <c r="P1" s="56" t="s">
         <v>59</v>
       </c>
     </row>
@@ -5944,52 +5941,52 @@
       </c>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" s="56">
+      <c r="A53" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="54">
         <v>611</v>
       </c>
       <c r="C53" s="53">
         <v>3.77</v>
       </c>
-      <c r="D53" s="54">
+      <c r="D53" s="53">
         <v>0.60399999999999998</v>
       </c>
       <c r="E53" s="53">
         <v>3.51</v>
       </c>
-      <c r="F53" s="54">
+      <c r="F53" s="53">
         <v>0.64800000000000002</v>
       </c>
       <c r="G53" s="53">
         <v>3.9034369885433704</v>
       </c>
-      <c r="H53" s="54">
+      <c r="H53" s="53">
         <v>0.70378635042468374</v>
       </c>
       <c r="I53" s="53">
         <v>2.92</v>
       </c>
-      <c r="J53" s="54">
+      <c r="J53" s="53">
         <v>0.93899999999999995</v>
       </c>
       <c r="K53" s="53">
         <v>3.82</v>
       </c>
-      <c r="L53" s="54">
+      <c r="L53" s="53">
         <v>0.61899999999999999</v>
       </c>
       <c r="M53" s="53">
         <v>3.73</v>
       </c>
-      <c r="N53" s="54">
+      <c r="N53" s="53">
         <v>0.69899999999999995</v>
       </c>
-      <c r="O53" s="55">
+      <c r="O53" s="85">
         <v>2.16</v>
       </c>
-      <c r="P53" s="58">
+      <c r="P53" s="86">
         <v>0.94</v>
       </c>
     </row>
@@ -7132,10 +7129,10 @@
       <c r="BL3" s="22">
         <v>0.63245553203367588</v>
       </c>
-      <c r="BM3" s="82">
+      <c r="BM3" s="79">
         <v>3</v>
       </c>
-      <c r="BN3" s="83">
+      <c r="BN3" s="80">
         <v>0.89442719099991586</v>
       </c>
       <c r="BO3" s="23">
@@ -7597,10 +7594,10 @@
       <c r="BL4" s="26">
         <v>0.89973541084243724</v>
       </c>
-      <c r="BM4" s="84">
+      <c r="BM4" s="81">
         <v>3.1428571428571428</v>
       </c>
-      <c r="BN4" s="85">
+      <c r="BN4" s="82">
         <v>1.3451854182690985</v>
       </c>
       <c r="BO4" s="27">
@@ -8062,10 +8059,10 @@
       <c r="BL5" s="26">
         <v>0.7988086367179803</v>
       </c>
-      <c r="BM5" s="84">
+      <c r="BM5" s="81">
         <v>3.5333333333333332</v>
       </c>
-      <c r="BN5" s="85">
+      <c r="BN5" s="82">
         <v>1.0600988273786192</v>
       </c>
       <c r="BO5" s="27">
@@ -8527,10 +8524,10 @@
       <c r="BL6" s="26">
         <v>0.54772255750516607</v>
       </c>
-      <c r="BM6" s="84">
+      <c r="BM6" s="81">
         <v>2.4</v>
       </c>
-      <c r="BN6" s="85">
+      <c r="BN6" s="82">
         <v>1.1401754250991378</v>
       </c>
       <c r="BO6" s="27">
@@ -8992,10 +8989,10 @@
       <c r="BL7" s="26">
         <v>0.56764621219754663</v>
       </c>
-      <c r="BM7" s="84">
+      <c r="BM7" s="81">
         <v>2.5999999999999996</v>
       </c>
-      <c r="BN7" s="85">
+      <c r="BN7" s="82">
         <v>1.0749676997731397</v>
       </c>
       <c r="BO7" s="27">
@@ -9457,10 +9454,10 @@
       <c r="BL8" s="26">
         <v>0.74754500159640203</v>
       </c>
-      <c r="BM8" s="84">
+      <c r="BM8" s="81">
         <v>3.1176470588235294</v>
       </c>
-      <c r="BN8" s="85">
+      <c r="BN8" s="82">
         <v>0.99261982533448267</v>
       </c>
       <c r="BO8" s="27">
@@ -9922,10 +9919,10 @@
       <c r="BL9" s="26">
         <v>0.44721359549995793</v>
       </c>
-      <c r="BM9" s="84">
+      <c r="BM9" s="81">
         <v>2.8</v>
       </c>
-      <c r="BN9" s="85">
+      <c r="BN9" s="82">
         <v>0.83666002653407556</v>
       </c>
       <c r="BO9" s="27">
@@ -10387,10 +10384,10 @@
       <c r="BL10" s="26">
         <v>0.47140452079103157</v>
       </c>
-      <c r="BM10" s="84">
+      <c r="BM10" s="81">
         <v>3.1</v>
       </c>
-      <c r="BN10" s="85">
+      <c r="BN10" s="82">
         <v>0.73786478737262184</v>
       </c>
       <c r="BO10" s="27">
@@ -10852,10 +10849,10 @@
       <c r="BL11" s="26">
         <v>0.90453403373329089</v>
       </c>
-      <c r="BM11" s="84">
+      <c r="BM11" s="81">
         <v>3</v>
       </c>
-      <c r="BN11" s="85">
+      <c r="BN11" s="82">
         <v>0.7745966692414834</v>
       </c>
       <c r="BO11" s="27">
@@ -11317,10 +11314,10 @@
       <c r="BL12" s="26">
         <v>1.1180339887498949</v>
       </c>
-      <c r="BM12" s="84">
+      <c r="BM12" s="81">
         <v>2.5555555555555554</v>
       </c>
-      <c r="BN12" s="85">
+      <c r="BN12" s="82">
         <v>1.0137937550497031</v>
       </c>
       <c r="BO12" s="27">
@@ -11782,10 +11779,10 @@
       <c r="BL13" s="26">
         <v>0.57735026918962573</v>
       </c>
-      <c r="BM13" s="84">
+      <c r="BM13" s="81">
         <v>1.6666666666666667</v>
       </c>
-      <c r="BN13" s="85">
+      <c r="BN13" s="82">
         <v>0.57735026918962573</v>
       </c>
       <c r="BO13" s="27">
@@ -12247,10 +12244,10 @@
       <c r="BL14" s="26">
         <v>0.75162162351482753</v>
       </c>
-      <c r="BM14" s="84">
+      <c r="BM14" s="81">
         <v>3.1818181818181821</v>
       </c>
-      <c r="BN14" s="85">
+      <c r="BN14" s="82">
         <v>0.85280286542244177</v>
       </c>
       <c r="BO14" s="27">
@@ -12712,10 +12709,10 @@
       <c r="BL15" s="26">
         <v>0.63245553203367588</v>
       </c>
-      <c r="BM15" s="84">
+      <c r="BM15" s="81">
         <v>3.1333333333333337</v>
       </c>
-      <c r="BN15" s="85">
+      <c r="BN15" s="82">
         <v>1.0600988273786194</v>
       </c>
       <c r="BO15" s="27">
@@ -13177,10 +13174,10 @@
       <c r="BL16" s="26">
         <v>0.89294371874630751</v>
       </c>
-      <c r="BM16" s="84">
+      <c r="BM16" s="81">
         <v>3.2121212121212119</v>
       </c>
-      <c r="BN16" s="85">
+      <c r="BN16" s="82">
         <v>1.1390120652778375</v>
       </c>
       <c r="BO16" s="27">
@@ -13642,10 +13639,10 @@
       <c r="BL17" s="26">
         <v>0.91387353346337541</v>
       </c>
-      <c r="BM17" s="84">
+      <c r="BM17" s="81">
         <v>3.3571428571428572</v>
       </c>
-      <c r="BN17" s="85">
+      <c r="BN17" s="82">
         <v>1.3363062095621219</v>
       </c>
       <c r="BO17" s="27">
@@ -14107,10 +14104,10 @@
       <c r="BL18" s="26">
         <v>0.44721359549995793</v>
       </c>
-      <c r="BM18" s="84">
+      <c r="BM18" s="81">
         <v>3</v>
       </c>
-      <c r="BN18" s="85">
+      <c r="BN18" s="82">
         <v>1.4142135623730949</v>
       </c>
       <c r="BO18" s="27">
@@ -14572,10 +14569,10 @@
       <c r="BL19" s="26">
         <v>1.1352924243950935</v>
       </c>
-      <c r="BM19" s="84">
+      <c r="BM19" s="81">
         <v>2.9</v>
       </c>
-      <c r="BN19" s="85">
+      <c r="BN19" s="82">
         <v>1.1972189997378648</v>
       </c>
       <c r="BO19" s="27">
@@ -15037,7 +15034,7 @@
       <c r="BL20" s="29">
         <v>0</v>
       </c>
-      <c r="BM20" s="84">
+      <c r="BM20" s="81">
         <v>3</v>
       </c>
       <c r="BN20" s="29">
@@ -15502,10 +15499,10 @@
       <c r="BL21" s="26">
         <v>1.0801234497346432</v>
       </c>
-      <c r="BM21" s="84">
+      <c r="BM21" s="81">
         <v>2.6999999999999997</v>
       </c>
-      <c r="BN21" s="85">
+      <c r="BN21" s="82">
         <v>0.82327260234856459</v>
       </c>
       <c r="BO21" s="27">
@@ -15967,10 +15964,10 @@
       <c r="BL22" s="26">
         <v>1.707825127659933</v>
       </c>
-      <c r="BM22" s="84">
+      <c r="BM22" s="81">
         <v>3.25</v>
       </c>
-      <c r="BN22" s="85">
+      <c r="BN22" s="82">
         <v>1.2583057392117916</v>
       </c>
       <c r="BO22" s="27">
@@ -16432,10 +16429,10 @@
       <c r="BL23" s="26">
         <v>0.91612538131290422</v>
       </c>
-      <c r="BM23" s="84">
+      <c r="BM23" s="81">
         <v>3</v>
       </c>
-      <c r="BN23" s="85">
+      <c r="BN23" s="82">
         <v>1.5118578920369088</v>
       </c>
       <c r="BO23" s="27">
@@ -16897,10 +16894,10 @@
       <c r="BL24" s="26">
         <v>0.75162162351482731</v>
       </c>
-      <c r="BM24" s="84">
+      <c r="BM24" s="81">
         <v>3.1818181818181821</v>
       </c>
-      <c r="BN24" s="85">
+      <c r="BN24" s="82">
         <v>0.85280286542244177</v>
       </c>
       <c r="BO24" s="27">
@@ -17362,10 +17359,10 @@
       <c r="BL25" s="26">
         <v>0</v>
       </c>
-      <c r="BM25" s="84">
+      <c r="BM25" s="81">
         <v>2.6</v>
       </c>
-      <c r="BN25" s="85">
+      <c r="BN25" s="82">
         <v>1.1401754250991381</v>
       </c>
       <c r="BO25" s="27">
@@ -17827,10 +17824,10 @@
       <c r="BL26" s="26">
         <v>1.0836246694508316</v>
       </c>
-      <c r="BM26" s="84">
+      <c r="BM26" s="81">
         <v>3.0833333333333335</v>
       </c>
-      <c r="BN26" s="85">
+      <c r="BN26" s="82">
         <v>1.164500152881315</v>
       </c>
       <c r="BO26" s="27">
@@ -18292,10 +18289,10 @@
       <c r="BL27" s="26">
         <v>0.44721359549995793</v>
       </c>
-      <c r="BM27" s="84">
+      <c r="BM27" s="81">
         <v>3.2</v>
       </c>
-      <c r="BN27" s="85">
+      <c r="BN27" s="82">
         <v>1.3038404810405297</v>
       </c>
       <c r="BO27" s="27">
@@ -18757,10 +18754,10 @@
       <c r="BL28" s="26">
         <v>0.54772255750516607</v>
       </c>
-      <c r="BM28" s="84">
+      <c r="BM28" s="81">
         <v>3.6</v>
       </c>
-      <c r="BN28" s="85">
+      <c r="BN28" s="82">
         <v>0.89442719099991586</v>
       </c>
       <c r="BO28" s="27">
@@ -19222,10 +19219,10 @@
       <c r="BL29" s="26">
         <v>1.4142135623730951</v>
       </c>
-      <c r="BM29" s="84">
+      <c r="BM29" s="81">
         <v>3.5</v>
       </c>
-      <c r="BN29" s="85">
+      <c r="BN29" s="82">
         <v>2.1213203435596424</v>
       </c>
       <c r="BO29" s="27">
@@ -19687,10 +19684,10 @@
       <c r="BL30" s="26">
         <v>0.7559289460184544</v>
       </c>
-      <c r="BM30" s="84">
+      <c r="BM30" s="81">
         <v>2.9999999999999996</v>
       </c>
-      <c r="BN30" s="85">
+      <c r="BN30" s="82">
         <v>1.0690449676496976</v>
       </c>
       <c r="BO30" s="27">
@@ -20152,10 +20149,10 @@
       <c r="BL31" s="26">
         <v>0.92680869599629834</v>
       </c>
-      <c r="BM31" s="84">
+      <c r="BM31" s="81">
         <v>2.6153846153846154</v>
       </c>
-      <c r="BN31" s="85">
+      <c r="BN31" s="82">
         <v>1.0439078454267836</v>
       </c>
       <c r="BO31" s="27">
@@ -20617,10 +20614,10 @@
       <c r="BL32" s="26">
         <v>0.752772652709081</v>
       </c>
-      <c r="BM32" s="84">
+      <c r="BM32" s="81">
         <v>2.6666666666666665</v>
       </c>
-      <c r="BN32" s="85">
+      <c r="BN32" s="82">
         <v>0.5163977794943222</v>
       </c>
       <c r="BO32" s="27">
@@ -21082,10 +21079,10 @@
       <c r="BL33" s="26">
         <v>0.83845386974128566</v>
       </c>
-      <c r="BM33" s="84">
+      <c r="BM33" s="81">
         <v>2.8148148148148149</v>
       </c>
-      <c r="BN33" s="85">
+      <c r="BN33" s="82">
         <v>1.0474420607937114</v>
       </c>
       <c r="BO33" s="27">
@@ -21547,10 +21544,10 @@
       <c r="BL34" s="26">
         <v>0.9759000729485332</v>
       </c>
-      <c r="BM34" s="84">
+      <c r="BM34" s="81">
         <v>3.5714285714285712</v>
       </c>
-      <c r="BN34" s="85">
+      <c r="BN34" s="82">
         <v>0.97590007294853331</v>
       </c>
       <c r="BO34" s="27">
@@ -22012,10 +22009,10 @@
       <c r="BL35" s="26">
         <v>0.66666666666666663</v>
       </c>
-      <c r="BM35" s="84">
+      <c r="BM35" s="81">
         <v>3.2</v>
       </c>
-      <c r="BN35" s="85">
+      <c r="BN35" s="82">
         <v>0.78881063774661553</v>
       </c>
       <c r="BO35" s="27">
@@ -22477,10 +22474,10 @@
       <c r="BL36" s="26">
         <v>0.99999999999999989</v>
       </c>
-      <c r="BM36" s="84">
+      <c r="BM36" s="81">
         <v>2</v>
       </c>
-      <c r="BN36" s="85">
+      <c r="BN36" s="82">
         <v>1.1547005383792515</v>
       </c>
       <c r="BO36" s="27">
@@ -22942,10 +22939,10 @@
       <c r="BL37" s="26">
         <v>0.83214969703748021</v>
       </c>
-      <c r="BM37" s="84">
+      <c r="BM37" s="81">
         <v>2.967741935483871</v>
       </c>
-      <c r="BN37" s="85">
+      <c r="BN37" s="82">
         <v>1.0160010160015238</v>
       </c>
       <c r="BO37" s="27">
@@ -23407,10 +23404,10 @@
       <c r="BL38" s="26">
         <v>0.56713087281560048</v>
       </c>
-      <c r="BM38" s="84">
+      <c r="BM38" s="81">
         <v>2.6315789473684217</v>
       </c>
-      <c r="BN38" s="85">
+      <c r="BN38" s="82">
         <v>0.76088591025268215</v>
       </c>
       <c r="BO38" s="27">
@@ -23872,10 +23869,10 @@
       <c r="BL39" s="26">
         <v>0.88191710368819676</v>
       </c>
-      <c r="BM39" s="84">
+      <c r="BM39" s="81">
         <v>3.3333333333333335</v>
       </c>
-      <c r="BN39" s="85">
+      <c r="BN39" s="82">
         <v>0.70710678118654757</v>
       </c>
       <c r="BO39" s="27">
@@ -24337,10 +24334,10 @@
       <c r="BL40" s="26">
         <v>0.53452248382484879</v>
       </c>
-      <c r="BM40" s="84">
+      <c r="BM40" s="81">
         <v>2.125</v>
       </c>
-      <c r="BN40" s="85">
+      <c r="BN40" s="82">
         <v>0.83452296039628016</v>
       </c>
       <c r="BO40" s="27">
@@ -24802,10 +24799,10 @@
       <c r="BL41" s="26">
         <v>1.1005049346146119</v>
       </c>
-      <c r="BM41" s="84">
+      <c r="BM41" s="81">
         <v>2.4000000000000004</v>
       </c>
-      <c r="BN41" s="85">
+      <c r="BN41" s="82">
         <v>0.96609178307929577</v>
       </c>
       <c r="BO41" s="27">
@@ -25267,10 +25264,10 @@
       <c r="BL42" s="26">
         <v>0.89442719099991586</v>
       </c>
-      <c r="BM42" s="84">
+      <c r="BM42" s="81">
         <v>2</v>
       </c>
-      <c r="BN42" s="85">
+      <c r="BN42" s="82">
         <v>0.70710678118654757</v>
       </c>
       <c r="BO42" s="27">
@@ -25732,10 +25729,10 @@
       <c r="BL43" s="26">
         <v>0.76729693648846842</v>
       </c>
-      <c r="BM43" s="84">
+      <c r="BM43" s="81">
         <v>3.045454545454545</v>
       </c>
-      <c r="BN43" s="85">
+      <c r="BN43" s="82">
         <v>0.95005126314183819</v>
       </c>
       <c r="BO43" s="27">
@@ -26197,10 +26194,10 @@
       <c r="BL44" s="26">
         <v>0.63245553203367577</v>
       </c>
-      <c r="BM44" s="84">
+      <c r="BM44" s="81">
         <v>3.1818181818181821</v>
       </c>
-      <c r="BN44" s="85">
+      <c r="BN44" s="82">
         <v>0.98164981721404276</v>
       </c>
       <c r="BO44" s="27">
@@ -26662,10 +26659,10 @@
       <c r="BL45" s="26">
         <v>0.96741792204684507</v>
       </c>
-      <c r="BM45" s="84">
+      <c r="BM45" s="81">
         <v>2.5384615384615383</v>
       </c>
-      <c r="BN45" s="85">
+      <c r="BN45" s="82">
         <v>1.1266014242982161</v>
       </c>
       <c r="BO45" s="27">
@@ -27127,10 +27124,10 @@
       <c r="BL46" s="26">
         <v>0.83333333333333326</v>
       </c>
-      <c r="BM46" s="84">
+      <c r="BM46" s="81">
         <v>4.1111111111111107</v>
       </c>
-      <c r="BN46" s="85">
+      <c r="BN46" s="82">
         <v>1.2692955176439846</v>
       </c>
       <c r="BO46" s="27">
@@ -27592,10 +27589,10 @@
       <c r="BL47" s="26">
         <v>0.88640526042791834</v>
       </c>
-      <c r="BM47" s="84">
+      <c r="BM47" s="81">
         <v>4.5</v>
       </c>
-      <c r="BN47" s="85">
+      <c r="BN47" s="82">
         <v>0.7559289460184544</v>
       </c>
       <c r="BO47" s="27">
@@ -28057,10 +28054,10 @@
       <c r="BL48" s="26">
         <v>0.79707442270319728</v>
       </c>
-      <c r="BM48" s="84">
+      <c r="BM48" s="81">
         <v>3.7777777777777772</v>
       </c>
-      <c r="BN48" s="85">
+      <c r="BN48" s="82">
         <v>1.3107054276032875</v>
       </c>
       <c r="BO48" s="27">
@@ -28522,10 +28519,10 @@
       <c r="BL49" s="26">
         <v>0.59673910628985094</v>
       </c>
-      <c r="BM49" s="84">
+      <c r="BM49" s="81">
         <v>4.0975609756097562</v>
       </c>
-      <c r="BN49" s="85">
+      <c r="BN49" s="82">
         <v>1.300093805246</v>
       </c>
       <c r="BO49" s="27">
@@ -28987,7 +28984,7 @@
       <c r="BL50" s="29">
         <v>0</v>
       </c>
-      <c r="BM50" s="84">
+      <c r="BM50" s="81">
         <v>5</v>
       </c>
       <c r="BN50" s="29">
@@ -29452,10 +29449,10 @@
       <c r="BL51" s="26">
         <v>0.92796072713833722</v>
       </c>
-      <c r="BM51" s="84">
+      <c r="BM51" s="81">
         <v>3.4444444444444446</v>
       </c>
-      <c r="BN51" s="85">
+      <c r="BN51" s="82">
         <v>1.5898986690282426</v>
       </c>
       <c r="BO51" s="27">
@@ -29917,10 +29914,10 @@
       <c r="BL52" s="32">
         <v>0.74322335295720665</v>
       </c>
-      <c r="BM52" s="84">
+      <c r="BM52" s="81">
         <v>4.4666666666666668</v>
       </c>
-      <c r="BN52" s="85">
+      <c r="BN52" s="82">
         <v>0.74322335295720654</v>
       </c>
       <c r="BO52" s="33">
@@ -30193,7 +30190,7 @@
       <c r="A53" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B53" s="56">
+      <c r="B53" s="54">
         <v>611</v>
       </c>
       <c r="C53" s="35">
@@ -30382,10 +30379,10 @@
       <c r="BL53" s="36">
         <v>0.87096135964821586</v>
       </c>
-      <c r="BM53" s="86">
+      <c r="BM53" s="83">
         <v>3.1538461538461546</v>
       </c>
-      <c r="BN53" s="87">
+      <c r="BN53" s="84">
         <v>1.1534257325700927</v>
       </c>
       <c r="BO53" s="37">

--- a/대시보드_구축_데이터.xlsx
+++ b/대시보드_구축_데이터.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\dashboard_v2\dashboard_v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\바탕 화면\MPLUS\세분화(휴학생 포함), 중도탈락에 휴학의도 제외\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4BD6E0-113F-426B-A768-2AF33AB0AB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{002F96B8-2FD0-4AA7-8EBD-E6EEF0CAECE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8805" yWindow="960" windowWidth="16770" windowHeight="12735" activeTab="1" xr2:uid="{3F0FD738-DFD1-4862-A6F4-1A909B15B620}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3F0FD738-DFD1-4862-A6F4-1A909B15B620}"/>
   </bookViews>
   <sheets>
     <sheet name="유형분류" sheetId="4" r:id="rId1"/>
@@ -322,9 +322,6 @@
     <t>우리 학교의 제도와 교육 프로그램은 만족스럽다.</t>
   </si>
   <si>
-    <t>나는 다른 대학에 진학했다면 더 좋았을 것이라고 생각한다.</t>
-  </si>
-  <si>
     <t>예상되는 나의 전공 교육내용에 흥미를 느낀다.</t>
   </si>
   <si>
@@ -470,6 +467,10 @@
   </si>
   <si>
     <t>행 N %</t>
+  </si>
+  <si>
+    <t>나는 다른 대학에 진학했다면 더 좋았을 것이라고 생각한다.*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1475,28 +1476,28 @@
         <v>8</v>
       </c>
       <c r="B1" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="E1" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="F1" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="G1" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="H1" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="I1" s="60" t="s">
         <v>138</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1" s="60" t="s">
-        <v>139</v>
       </c>
       <c r="J1" s="60" t="s">
         <v>0</v>
@@ -1510,34 +1511,34 @@
         <v>8</v>
       </c>
       <c r="B2" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="63" t="s">
-        <v>141</v>
-      </c>
       <c r="D2" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="E2" s="63" t="s">
-        <v>141</v>
-      </c>
       <c r="F2" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="63" t="s">
-        <v>141</v>
-      </c>
       <c r="H2" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="I2" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="63" t="s">
-        <v>141</v>
-      </c>
       <c r="J2" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="K2" s="64" t="s">
         <v>140</v>
-      </c>
-      <c r="K2" s="64" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -6200,82 +6201,82 @@
         <v>91</v>
       </c>
       <c r="BM1" t="s">
+        <v>141</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>141</v>
+      </c>
+      <c r="BO1" t="s">
         <v>92</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>92</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>93</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>93</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>94</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>94</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" t="s">
         <v>95</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BV1" t="s">
         <v>95</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BW1" t="s">
         <v>96</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BX1" t="s">
         <v>96</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BY1" t="s">
         <v>97</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BZ1" t="s">
         <v>97</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="CA1" t="s">
         <v>98</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CB1" t="s">
         <v>98</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CC1" t="s">
         <v>99</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>99</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CE1" t="s">
         <v>100</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>100</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>101</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>101</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>102</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>102</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>103</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CL1" t="s">
         <v>103</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>104</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>104</v>
       </c>
       <c r="CM1" t="s">
         <v>5</v>
@@ -6284,190 +6285,190 @@
         <v>5</v>
       </c>
       <c r="CO1" t="s">
+        <v>104</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>104</v>
+      </c>
+      <c r="CQ1" t="s">
         <v>105</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
         <v>105</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CS1" t="s">
         <v>106</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CT1" t="s">
         <v>106</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>107</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>107</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>108</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CX1" t="s">
         <v>108</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CY1" t="s">
         <v>109</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CZ1" t="s">
         <v>109</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DA1" t="s">
         <v>110</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DB1" t="s">
         <v>110</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DC1" t="s">
         <v>111</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DD1" t="s">
         <v>111</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DE1" t="s">
         <v>112</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DF1" t="s">
         <v>112</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DG1" t="s">
         <v>113</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>113</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>114</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DJ1" t="s">
         <v>114</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DK1" t="s">
         <v>115</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DL1" t="s">
         <v>115</v>
       </c>
-      <c r="DK1" t="s">
+      <c r="DM1" t="s">
         <v>116</v>
       </c>
-      <c r="DL1" t="s">
+      <c r="DN1" t="s">
         <v>116</v>
       </c>
-      <c r="DM1" t="s">
+      <c r="DO1" t="s">
         <v>117</v>
       </c>
-      <c r="DN1" t="s">
+      <c r="DP1" t="s">
         <v>117</v>
       </c>
-      <c r="DO1" t="s">
+      <c r="DQ1" t="s">
         <v>118</v>
       </c>
-      <c r="DP1" t="s">
+      <c r="DR1" t="s">
         <v>118</v>
       </c>
-      <c r="DQ1" t="s">
+      <c r="DS1" t="s">
         <v>119</v>
       </c>
-      <c r="DR1" t="s">
+      <c r="DT1" t="s">
         <v>119</v>
       </c>
-      <c r="DS1" t="s">
+      <c r="DU1" t="s">
         <v>120</v>
       </c>
-      <c r="DT1" t="s">
+      <c r="DV1" t="s">
         <v>120</v>
       </c>
-      <c r="DU1" t="s">
+      <c r="DW1" t="s">
         <v>121</v>
       </c>
-      <c r="DV1" t="s">
+      <c r="DX1" t="s">
         <v>121</v>
       </c>
-      <c r="DW1" t="s">
+      <c r="DY1" t="s">
         <v>122</v>
       </c>
-      <c r="DX1" t="s">
+      <c r="DZ1" t="s">
         <v>122</v>
       </c>
-      <c r="DY1" t="s">
+      <c r="EA1" t="s">
         <v>123</v>
       </c>
-      <c r="DZ1" t="s">
+      <c r="EB1" t="s">
         <v>123</v>
       </c>
-      <c r="EA1" t="s">
+      <c r="EC1" t="s">
         <v>124</v>
       </c>
-      <c r="EB1" t="s">
+      <c r="ED1" t="s">
         <v>124</v>
       </c>
-      <c r="EC1" t="s">
+      <c r="EE1" t="s">
         <v>125</v>
       </c>
-      <c r="ED1" t="s">
+      <c r="EF1" t="s">
         <v>125</v>
       </c>
-      <c r="EE1" t="s">
+      <c r="EG1" t="s">
         <v>126</v>
       </c>
-      <c r="EF1" t="s">
+      <c r="EH1" t="s">
         <v>126</v>
       </c>
-      <c r="EG1" t="s">
+      <c r="EI1" t="s">
         <v>127</v>
       </c>
-      <c r="EH1" t="s">
+      <c r="EJ1" t="s">
         <v>127</v>
       </c>
-      <c r="EI1" t="s">
+      <c r="EK1" t="s">
         <v>128</v>
       </c>
-      <c r="EJ1" t="s">
+      <c r="EL1" t="s">
         <v>128</v>
       </c>
-      <c r="EK1" t="s">
+      <c r="EM1" t="s">
         <v>129</v>
       </c>
-      <c r="EL1" t="s">
+      <c r="EN1" t="s">
         <v>129</v>
       </c>
-      <c r="EM1" t="s">
+      <c r="EO1" t="s">
         <v>130</v>
       </c>
-      <c r="EN1" t="s">
+      <c r="EP1" t="s">
         <v>130</v>
       </c>
-      <c r="EO1" t="s">
+      <c r="EQ1" t="s">
         <v>131</v>
       </c>
-      <c r="EP1" t="s">
+      <c r="ER1" t="s">
         <v>131</v>
       </c>
-      <c r="EQ1" t="s">
+      <c r="ES1" t="s">
         <v>132</v>
       </c>
-      <c r="ER1" t="s">
+      <c r="ET1" t="s">
         <v>132</v>
       </c>
-      <c r="ES1" t="s">
+      <c r="EU1" t="s">
         <v>133</v>
       </c>
-      <c r="ET1" t="s">
+      <c r="EV1" t="s">
         <v>133</v>
       </c>
-      <c r="EU1" t="s">
+      <c r="EW1" t="s">
         <v>134</v>
       </c>
-      <c r="EV1" t="s">
+      <c r="EX1" t="s">
         <v>134</v>
-      </c>
-      <c r="EW1" t="s">
-        <v>135</v>
-      </c>
-      <c r="EX1" t="s">
-        <v>135</v>
       </c>
       <c r="EY1" s="46"/>
     </row>
